--- a/web/public/forms/hyeonjang-jojikdo.xlsx
+++ b/web/public/forms/hyeonjang-jojikdo.xlsx
@@ -8,9 +8,11 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="현장 조직도 · 비상 조직도" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="작성 예시" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'현장 조직도 · 비상 조직도'!$A$1:$X$47</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'현장 조직도 · 비상 조직도'!$A$1:$X$44</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'작성 예시'!$A$1:$X$44</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -18,8 +20,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="6">
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="#,##0;[Red]-#,##0;&quot;&quot;"/>
+    <numFmt numFmtId="165" formatCode="yyyy&quot;년&quot; m&quot;월&quot; d&quot;일&quot;"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+  </numFmts>
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,29 +37,50 @@
       <name val="맑은 고딕"/>
       <b val="1"/>
       <color rgb="000F203F"/>
-      <sz val="10.5"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
-      <color rgb="00222222"/>
+      <color rgb="006B7280"/>
       <sz val="8.5"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
-      <color rgb="000F203F"/>
+      <color rgb="00111827"/>
       <sz val="19"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
-      <color rgb="000F203F"/>
+      <color rgb="001F2937"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
-      <color rgb="00222222"/>
+      <color rgb="00000000"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="001F2937"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="001F2937"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="4">
@@ -65,12 +92,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F6F8FC"/>
+        <fgColor rgb="00F3F5F9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EEF3FB"/>
+        <fgColor rgb="00E8EEF7"/>
       </patternFill>
     </fill>
   </fills>
@@ -84,23 +111,23 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00BFC7D5"/>
+        <color rgb="005B6573"/>
       </left>
       <right style="thin">
-        <color rgb="00BFC7D5"/>
+        <color rgb="005B6573"/>
       </right>
       <top style="thin">
-        <color rgb="00BFC7D5"/>
+        <color rgb="005B6573"/>
       </top>
       <bottom style="thin">
-        <color rgb="00BFC7D5"/>
+        <color rgb="005B6573"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -109,32 +136,53 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -501,7 +549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:X50"/>
+  <dimension ref="A1:X47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3.6" customWidth="1" min="1" max="1"/>
@@ -530,15 +578,15 @@
     <col width="3.6" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
+    <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵   |   k-conmap.com   무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="M1" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">← 이 1행을 지우고 쓰셔도 됩니다   </t>
+          <t xml:space="preserve">← 이 1행을 지우고 쓰셔도 됩니다  </t>
         </is>
       </c>
     </row>
@@ -562,7 +610,7 @@
       <c r="D5" s="5" t="n"/>
       <c r="E5" s="5" t="n"/>
       <c r="F5" s="5" t="n"/>
-      <c r="G5" s="6" t="inlineStr"/>
+      <c r="G5" s="6" t="n"/>
       <c r="H5" s="5" t="n"/>
       <c r="I5" s="5" t="n"/>
       <c r="J5" s="5" t="n"/>
@@ -592,7 +640,7 @@
       <c r="D6" s="5" t="n"/>
       <c r="E6" s="5" t="n"/>
       <c r="F6" s="5" t="n"/>
-      <c r="G6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="n"/>
       <c r="H6" s="5" t="n"/>
       <c r="I6" s="5" t="n"/>
       <c r="J6" s="5" t="n"/>
@@ -622,7 +670,7 @@
       <c r="D7" s="5" t="n"/>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
-      <c r="G7" s="6" t="inlineStr"/>
+      <c r="G7" s="7" t="n"/>
       <c r="H7" s="5" t="n"/>
       <c r="I7" s="5" t="n"/>
       <c r="J7" s="5" t="n"/>
@@ -652,7 +700,7 @@
       <c r="D8" s="5" t="n"/>
       <c r="E8" s="5" t="n"/>
       <c r="F8" s="5" t="n"/>
-      <c r="G8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="n"/>
       <c r="H8" s="5" t="n"/>
       <c r="I8" s="5" t="n"/>
       <c r="J8" s="5" t="n"/>
@@ -682,7 +730,7 @@
       <c r="D9" s="5" t="n"/>
       <c r="E9" s="5" t="n"/>
       <c r="F9" s="5" t="n"/>
-      <c r="G9" s="6" t="inlineStr"/>
+      <c r="G9" s="8" t="n"/>
       <c r="H9" s="5" t="n"/>
       <c r="I9" s="5" t="n"/>
       <c r="J9" s="5" t="n"/>
@@ -703,7 +751,7 @@
     </row>
     <row r="10" ht="6" customHeight="1"/>
     <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>■ 평상시 조직</t>
         </is>
@@ -711,7 +759,7 @@
     </row>
     <row r="12" ht="6" customHeight="1"/>
     <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
@@ -719,7 +767,7 @@
       <c r="B13" s="5" t="n"/>
       <c r="C13" s="5" t="n"/>
       <c r="D13" s="5" t="n"/>
-      <c r="E13" s="8" t="inlineStr">
+      <c r="E13" s="10" t="inlineStr">
         <is>
           <t>직책</t>
         </is>
@@ -727,7 +775,7 @@
       <c r="F13" s="5" t="n"/>
       <c r="G13" s="5" t="n"/>
       <c r="H13" s="5" t="n"/>
-      <c r="I13" s="8" t="inlineStr">
+      <c r="I13" s="10" t="inlineStr">
         <is>
           <t>성명</t>
         </is>
@@ -735,7 +783,7 @@
       <c r="J13" s="5" t="n"/>
       <c r="K13" s="5" t="n"/>
       <c r="L13" s="5" t="n"/>
-      <c r="M13" s="8" t="inlineStr">
+      <c r="M13" s="10" t="inlineStr">
         <is>
           <t>담당 업무</t>
         </is>
@@ -746,7 +794,7 @@
       <c r="Q13" s="5" t="n"/>
       <c r="R13" s="5" t="n"/>
       <c r="S13" s="5" t="n"/>
-      <c r="T13" s="8" t="inlineStr">
+      <c r="T13" s="10" t="inlineStr">
         <is>
           <t>연락처</t>
         </is>
@@ -757,298 +805,302 @@
       <c r="X13" s="5" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="9" t="inlineStr"/>
+      <c r="A14" s="11" t="n"/>
       <c r="B14" s="5" t="n"/>
       <c r="C14" s="5" t="n"/>
       <c r="D14" s="5" t="n"/>
-      <c r="E14" s="9" t="inlineStr"/>
+      <c r="E14" s="11" t="n"/>
       <c r="F14" s="5" t="n"/>
       <c r="G14" s="5" t="n"/>
       <c r="H14" s="5" t="n"/>
-      <c r="I14" s="9" t="inlineStr"/>
+      <c r="I14" s="11" t="n"/>
       <c r="J14" s="5" t="n"/>
       <c r="K14" s="5" t="n"/>
       <c r="L14" s="5" t="n"/>
-      <c r="M14" s="9" t="inlineStr"/>
+      <c r="M14" s="12" t="n"/>
       <c r="N14" s="5" t="n"/>
       <c r="O14" s="5" t="n"/>
       <c r="P14" s="5" t="n"/>
       <c r="Q14" s="5" t="n"/>
       <c r="R14" s="5" t="n"/>
       <c r="S14" s="5" t="n"/>
-      <c r="T14" s="9" t="inlineStr"/>
+      <c r="T14" s="11" t="n"/>
       <c r="U14" s="5" t="n"/>
       <c r="V14" s="5" t="n"/>
       <c r="W14" s="5" t="n"/>
       <c r="X14" s="5" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="9" t="inlineStr"/>
+      <c r="A15" s="11" t="n"/>
       <c r="B15" s="5" t="n"/>
       <c r="C15" s="5" t="n"/>
       <c r="D15" s="5" t="n"/>
-      <c r="E15" s="9" t="inlineStr"/>
+      <c r="E15" s="11" t="n"/>
       <c r="F15" s="5" t="n"/>
       <c r="G15" s="5" t="n"/>
       <c r="H15" s="5" t="n"/>
-      <c r="I15" s="9" t="inlineStr"/>
+      <c r="I15" s="11" t="n"/>
       <c r="J15" s="5" t="n"/>
       <c r="K15" s="5" t="n"/>
       <c r="L15" s="5" t="n"/>
-      <c r="M15" s="9" t="inlineStr"/>
+      <c r="M15" s="12" t="n"/>
       <c r="N15" s="5" t="n"/>
       <c r="O15" s="5" t="n"/>
       <c r="P15" s="5" t="n"/>
       <c r="Q15" s="5" t="n"/>
       <c r="R15" s="5" t="n"/>
       <c r="S15" s="5" t="n"/>
-      <c r="T15" s="9" t="inlineStr"/>
+      <c r="T15" s="11" t="n"/>
       <c r="U15" s="5" t="n"/>
       <c r="V15" s="5" t="n"/>
       <c r="W15" s="5" t="n"/>
       <c r="X15" s="5" t="n"/>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="9" t="inlineStr"/>
+      <c r="A16" s="11" t="n"/>
       <c r="B16" s="5" t="n"/>
       <c r="C16" s="5" t="n"/>
       <c r="D16" s="5" t="n"/>
-      <c r="E16" s="9" t="inlineStr"/>
+      <c r="E16" s="11" t="n"/>
       <c r="F16" s="5" t="n"/>
       <c r="G16" s="5" t="n"/>
       <c r="H16" s="5" t="n"/>
-      <c r="I16" s="9" t="inlineStr"/>
+      <c r="I16" s="11" t="n"/>
       <c r="J16" s="5" t="n"/>
       <c r="K16" s="5" t="n"/>
       <c r="L16" s="5" t="n"/>
-      <c r="M16" s="9" t="inlineStr"/>
+      <c r="M16" s="12" t="n"/>
       <c r="N16" s="5" t="n"/>
       <c r="O16" s="5" t="n"/>
       <c r="P16" s="5" t="n"/>
       <c r="Q16" s="5" t="n"/>
       <c r="R16" s="5" t="n"/>
       <c r="S16" s="5" t="n"/>
-      <c r="T16" s="9" t="inlineStr"/>
+      <c r="T16" s="11" t="n"/>
       <c r="U16" s="5" t="n"/>
       <c r="V16" s="5" t="n"/>
       <c r="W16" s="5" t="n"/>
       <c r="X16" s="5" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="9" t="inlineStr"/>
+      <c r="A17" s="11" t="n"/>
       <c r="B17" s="5" t="n"/>
       <c r="C17" s="5" t="n"/>
       <c r="D17" s="5" t="n"/>
-      <c r="E17" s="9" t="inlineStr"/>
+      <c r="E17" s="11" t="n"/>
       <c r="F17" s="5" t="n"/>
       <c r="G17" s="5" t="n"/>
       <c r="H17" s="5" t="n"/>
-      <c r="I17" s="9" t="inlineStr"/>
+      <c r="I17" s="11" t="n"/>
       <c r="J17" s="5" t="n"/>
       <c r="K17" s="5" t="n"/>
       <c r="L17" s="5" t="n"/>
-      <c r="M17" s="9" t="inlineStr"/>
+      <c r="M17" s="12" t="n"/>
       <c r="N17" s="5" t="n"/>
       <c r="O17" s="5" t="n"/>
       <c r="P17" s="5" t="n"/>
       <c r="Q17" s="5" t="n"/>
       <c r="R17" s="5" t="n"/>
       <c r="S17" s="5" t="n"/>
-      <c r="T17" s="9" t="inlineStr"/>
+      <c r="T17" s="11" t="n"/>
       <c r="U17" s="5" t="n"/>
       <c r="V17" s="5" t="n"/>
       <c r="W17" s="5" t="n"/>
       <c r="X17" s="5" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="9" t="inlineStr"/>
+      <c r="A18" s="11" t="n"/>
       <c r="B18" s="5" t="n"/>
       <c r="C18" s="5" t="n"/>
       <c r="D18" s="5" t="n"/>
-      <c r="E18" s="9" t="inlineStr"/>
+      <c r="E18" s="11" t="n"/>
       <c r="F18" s="5" t="n"/>
       <c r="G18" s="5" t="n"/>
       <c r="H18" s="5" t="n"/>
-      <c r="I18" s="9" t="inlineStr"/>
+      <c r="I18" s="11" t="n"/>
       <c r="J18" s="5" t="n"/>
       <c r="K18" s="5" t="n"/>
       <c r="L18" s="5" t="n"/>
-      <c r="M18" s="9" t="inlineStr"/>
+      <c r="M18" s="12" t="n"/>
       <c r="N18" s="5" t="n"/>
       <c r="O18" s="5" t="n"/>
       <c r="P18" s="5" t="n"/>
       <c r="Q18" s="5" t="n"/>
       <c r="R18" s="5" t="n"/>
       <c r="S18" s="5" t="n"/>
-      <c r="T18" s="9" t="inlineStr"/>
+      <c r="T18" s="11" t="n"/>
       <c r="U18" s="5" t="n"/>
       <c r="V18" s="5" t="n"/>
       <c r="W18" s="5" t="n"/>
       <c r="X18" s="5" t="n"/>
     </row>
     <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="9" t="inlineStr"/>
+      <c r="A19" s="11" t="n"/>
       <c r="B19" s="5" t="n"/>
       <c r="C19" s="5" t="n"/>
       <c r="D19" s="5" t="n"/>
-      <c r="E19" s="9" t="inlineStr"/>
+      <c r="E19" s="11" t="n"/>
       <c r="F19" s="5" t="n"/>
       <c r="G19" s="5" t="n"/>
       <c r="H19" s="5" t="n"/>
-      <c r="I19" s="9" t="inlineStr"/>
+      <c r="I19" s="11" t="n"/>
       <c r="J19" s="5" t="n"/>
       <c r="K19" s="5" t="n"/>
       <c r="L19" s="5" t="n"/>
-      <c r="M19" s="9" t="inlineStr"/>
+      <c r="M19" s="12" t="n"/>
       <c r="N19" s="5" t="n"/>
       <c r="O19" s="5" t="n"/>
       <c r="P19" s="5" t="n"/>
       <c r="Q19" s="5" t="n"/>
       <c r="R19" s="5" t="n"/>
       <c r="S19" s="5" t="n"/>
-      <c r="T19" s="9" t="inlineStr"/>
+      <c r="T19" s="11" t="n"/>
       <c r="U19" s="5" t="n"/>
       <c r="V19" s="5" t="n"/>
       <c r="W19" s="5" t="n"/>
       <c r="X19" s="5" t="n"/>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="9" t="inlineStr"/>
+      <c r="A20" s="11" t="n"/>
       <c r="B20" s="5" t="n"/>
       <c r="C20" s="5" t="n"/>
       <c r="D20" s="5" t="n"/>
-      <c r="E20" s="9" t="inlineStr"/>
+      <c r="E20" s="11" t="n"/>
       <c r="F20" s="5" t="n"/>
       <c r="G20" s="5" t="n"/>
       <c r="H20" s="5" t="n"/>
-      <c r="I20" s="9" t="inlineStr"/>
+      <c r="I20" s="11" t="n"/>
       <c r="J20" s="5" t="n"/>
       <c r="K20" s="5" t="n"/>
       <c r="L20" s="5" t="n"/>
-      <c r="M20" s="9" t="inlineStr"/>
+      <c r="M20" s="12" t="n"/>
       <c r="N20" s="5" t="n"/>
       <c r="O20" s="5" t="n"/>
       <c r="P20" s="5" t="n"/>
       <c r="Q20" s="5" t="n"/>
       <c r="R20" s="5" t="n"/>
       <c r="S20" s="5" t="n"/>
-      <c r="T20" s="9" t="inlineStr"/>
+      <c r="T20" s="11" t="n"/>
       <c r="U20" s="5" t="n"/>
       <c r="V20" s="5" t="n"/>
       <c r="W20" s="5" t="n"/>
       <c r="X20" s="5" t="n"/>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="9" t="inlineStr"/>
+      <c r="A21" s="11" t="n"/>
       <c r="B21" s="5" t="n"/>
       <c r="C21" s="5" t="n"/>
       <c r="D21" s="5" t="n"/>
-      <c r="E21" s="9" t="inlineStr"/>
+      <c r="E21" s="11" t="n"/>
       <c r="F21" s="5" t="n"/>
       <c r="G21" s="5" t="n"/>
       <c r="H21" s="5" t="n"/>
-      <c r="I21" s="9" t="inlineStr"/>
+      <c r="I21" s="11" t="n"/>
       <c r="J21" s="5" t="n"/>
       <c r="K21" s="5" t="n"/>
       <c r="L21" s="5" t="n"/>
-      <c r="M21" s="9" t="inlineStr"/>
+      <c r="M21" s="12" t="n"/>
       <c r="N21" s="5" t="n"/>
       <c r="O21" s="5" t="n"/>
       <c r="P21" s="5" t="n"/>
       <c r="Q21" s="5" t="n"/>
       <c r="R21" s="5" t="n"/>
       <c r="S21" s="5" t="n"/>
-      <c r="T21" s="9" t="inlineStr"/>
+      <c r="T21" s="11" t="n"/>
       <c r="U21" s="5" t="n"/>
       <c r="V21" s="5" t="n"/>
       <c r="W21" s="5" t="n"/>
       <c r="X21" s="5" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="9" t="inlineStr"/>
+      <c r="A22" s="11" t="n"/>
       <c r="B22" s="5" t="n"/>
       <c r="C22" s="5" t="n"/>
       <c r="D22" s="5" t="n"/>
-      <c r="E22" s="9" t="inlineStr"/>
+      <c r="E22" s="11" t="n"/>
       <c r="F22" s="5" t="n"/>
       <c r="G22" s="5" t="n"/>
       <c r="H22" s="5" t="n"/>
-      <c r="I22" s="9" t="inlineStr"/>
+      <c r="I22" s="11" t="n"/>
       <c r="J22" s="5" t="n"/>
       <c r="K22" s="5" t="n"/>
       <c r="L22" s="5" t="n"/>
-      <c r="M22" s="9" t="inlineStr"/>
+      <c r="M22" s="12" t="n"/>
       <c r="N22" s="5" t="n"/>
       <c r="O22" s="5" t="n"/>
       <c r="P22" s="5" t="n"/>
       <c r="Q22" s="5" t="n"/>
       <c r="R22" s="5" t="n"/>
       <c r="S22" s="5" t="n"/>
-      <c r="T22" s="9" t="inlineStr"/>
+      <c r="T22" s="11" t="n"/>
       <c r="U22" s="5" t="n"/>
       <c r="V22" s="5" t="n"/>
       <c r="W22" s="5" t="n"/>
       <c r="X22" s="5" t="n"/>
     </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="9" t="inlineStr"/>
-      <c r="B23" s="5" t="n"/>
-      <c r="C23" s="5" t="n"/>
-      <c r="D23" s="5" t="n"/>
-      <c r="E23" s="9" t="inlineStr"/>
-      <c r="F23" s="5" t="n"/>
-      <c r="G23" s="5" t="n"/>
-      <c r="H23" s="5" t="n"/>
-      <c r="I23" s="9" t="inlineStr"/>
-      <c r="J23" s="5" t="n"/>
-      <c r="K23" s="5" t="n"/>
-      <c r="L23" s="5" t="n"/>
-      <c r="M23" s="9" t="inlineStr"/>
-      <c r="N23" s="5" t="n"/>
-      <c r="O23" s="5" t="n"/>
-      <c r="P23" s="5" t="n"/>
-      <c r="Q23" s="5" t="n"/>
-      <c r="R23" s="5" t="n"/>
-      <c r="S23" s="5" t="n"/>
-      <c r="T23" s="9" t="inlineStr"/>
-      <c r="U23" s="5" t="n"/>
-      <c r="V23" s="5" t="n"/>
-      <c r="W23" s="5" t="n"/>
-      <c r="X23" s="5" t="n"/>
-    </row>
-    <row r="24" ht="6" customHeight="1"/>
-    <row r="25" ht="26" customHeight="1">
-      <c r="A25" s="7" t="inlineStr">
+    <row r="23" ht="6" customHeight="1"/>
+    <row r="24" ht="26" customHeight="1">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>■ 비상시 조직 (사고·재해 발생 시)</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="6" customHeight="1"/>
-    <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="8" t="inlineStr">
+    <row r="25" ht="6" customHeight="1"/>
+    <row r="26" ht="24" customHeight="1">
+      <c r="A26" s="10" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="5" t="n"/>
+      <c r="D26" s="5" t="n"/>
+      <c r="E26" s="10" t="inlineStr">
+        <is>
+          <t>직책·성명</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="n"/>
+      <c r="G26" s="5" t="n"/>
+      <c r="H26" s="5" t="n"/>
+      <c r="I26" s="5" t="n"/>
+      <c r="J26" s="5" t="n"/>
+      <c r="K26" s="10" t="inlineStr">
+        <is>
+          <t>비상시 임무</t>
+        </is>
+      </c>
+      <c r="L26" s="5" t="n"/>
+      <c r="M26" s="5" t="n"/>
+      <c r="N26" s="5" t="n"/>
+      <c r="O26" s="5" t="n"/>
+      <c r="P26" s="5" t="n"/>
+      <c r="Q26" s="5" t="n"/>
+      <c r="R26" s="5" t="n"/>
+      <c r="S26" s="10" t="inlineStr">
+        <is>
+          <t>연락처</t>
+        </is>
+      </c>
+      <c r="T26" s="5" t="n"/>
+      <c r="U26" s="5" t="n"/>
+      <c r="V26" s="5" t="n"/>
+      <c r="W26" s="5" t="n"/>
+      <c r="X26" s="5" t="n"/>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="11" t="n"/>
       <c r="B27" s="5" t="n"/>
       <c r="C27" s="5" t="n"/>
       <c r="D27" s="5" t="n"/>
-      <c r="E27" s="8" t="inlineStr">
-        <is>
-          <t>직책·성명</t>
-        </is>
-      </c>
+      <c r="E27" s="12" t="n"/>
       <c r="F27" s="5" t="n"/>
       <c r="G27" s="5" t="n"/>
       <c r="H27" s="5" t="n"/>
       <c r="I27" s="5" t="n"/>
       <c r="J27" s="5" t="n"/>
-      <c r="K27" s="8" t="inlineStr">
-        <is>
-          <t>비상시 임무</t>
-        </is>
-      </c>
+      <c r="K27" s="12" t="n"/>
       <c r="L27" s="5" t="n"/>
       <c r="M27" s="5" t="n"/>
       <c r="N27" s="5" t="n"/>
@@ -1056,11 +1108,7 @@
       <c r="P27" s="5" t="n"/>
       <c r="Q27" s="5" t="n"/>
       <c r="R27" s="5" t="n"/>
-      <c r="S27" s="8" t="inlineStr">
-        <is>
-          <t>연락처</t>
-        </is>
-      </c>
+      <c r="S27" s="12" t="n"/>
       <c r="T27" s="5" t="n"/>
       <c r="U27" s="5" t="n"/>
       <c r="V27" s="5" t="n"/>
@@ -1068,17 +1116,17 @@
       <c r="X27" s="5" t="n"/>
     </row>
     <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="9" t="inlineStr"/>
+      <c r="A28" s="11" t="n"/>
       <c r="B28" s="5" t="n"/>
       <c r="C28" s="5" t="n"/>
       <c r="D28" s="5" t="n"/>
-      <c r="E28" s="9" t="inlineStr"/>
+      <c r="E28" s="12" t="n"/>
       <c r="F28" s="5" t="n"/>
       <c r="G28" s="5" t="n"/>
       <c r="H28" s="5" t="n"/>
       <c r="I28" s="5" t="n"/>
       <c r="J28" s="5" t="n"/>
-      <c r="K28" s="9" t="inlineStr"/>
+      <c r="K28" s="12" t="n"/>
       <c r="L28" s="5" t="n"/>
       <c r="M28" s="5" t="n"/>
       <c r="N28" s="5" t="n"/>
@@ -1086,7 +1134,7 @@
       <c r="P28" s="5" t="n"/>
       <c r="Q28" s="5" t="n"/>
       <c r="R28" s="5" t="n"/>
-      <c r="S28" s="9" t="inlineStr"/>
+      <c r="S28" s="12" t="n"/>
       <c r="T28" s="5" t="n"/>
       <c r="U28" s="5" t="n"/>
       <c r="V28" s="5" t="n"/>
@@ -1094,17 +1142,17 @@
       <c r="X28" s="5" t="n"/>
     </row>
     <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="9" t="inlineStr"/>
+      <c r="A29" s="11" t="n"/>
       <c r="B29" s="5" t="n"/>
       <c r="C29" s="5" t="n"/>
       <c r="D29" s="5" t="n"/>
-      <c r="E29" s="9" t="inlineStr"/>
+      <c r="E29" s="12" t="n"/>
       <c r="F29" s="5" t="n"/>
       <c r="G29" s="5" t="n"/>
       <c r="H29" s="5" t="n"/>
       <c r="I29" s="5" t="n"/>
       <c r="J29" s="5" t="n"/>
-      <c r="K29" s="9" t="inlineStr"/>
+      <c r="K29" s="12" t="n"/>
       <c r="L29" s="5" t="n"/>
       <c r="M29" s="5" t="n"/>
       <c r="N29" s="5" t="n"/>
@@ -1112,7 +1160,7 @@
       <c r="P29" s="5" t="n"/>
       <c r="Q29" s="5" t="n"/>
       <c r="R29" s="5" t="n"/>
-      <c r="S29" s="9" t="inlineStr"/>
+      <c r="S29" s="12" t="n"/>
       <c r="T29" s="5" t="n"/>
       <c r="U29" s="5" t="n"/>
       <c r="V29" s="5" t="n"/>
@@ -1120,17 +1168,17 @@
       <c r="X29" s="5" t="n"/>
     </row>
     <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="9" t="inlineStr"/>
+      <c r="A30" s="11" t="n"/>
       <c r="B30" s="5" t="n"/>
       <c r="C30" s="5" t="n"/>
       <c r="D30" s="5" t="n"/>
-      <c r="E30" s="9" t="inlineStr"/>
+      <c r="E30" s="12" t="n"/>
       <c r="F30" s="5" t="n"/>
       <c r="G30" s="5" t="n"/>
       <c r="H30" s="5" t="n"/>
       <c r="I30" s="5" t="n"/>
       <c r="J30" s="5" t="n"/>
-      <c r="K30" s="9" t="inlineStr"/>
+      <c r="K30" s="12" t="n"/>
       <c r="L30" s="5" t="n"/>
       <c r="M30" s="5" t="n"/>
       <c r="N30" s="5" t="n"/>
@@ -1138,7 +1186,7 @@
       <c r="P30" s="5" t="n"/>
       <c r="Q30" s="5" t="n"/>
       <c r="R30" s="5" t="n"/>
-      <c r="S30" s="9" t="inlineStr"/>
+      <c r="S30" s="12" t="n"/>
       <c r="T30" s="5" t="n"/>
       <c r="U30" s="5" t="n"/>
       <c r="V30" s="5" t="n"/>
@@ -1146,17 +1194,17 @@
       <c r="X30" s="5" t="n"/>
     </row>
     <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="9" t="inlineStr"/>
+      <c r="A31" s="11" t="n"/>
       <c r="B31" s="5" t="n"/>
       <c r="C31" s="5" t="n"/>
       <c r="D31" s="5" t="n"/>
-      <c r="E31" s="9" t="inlineStr"/>
+      <c r="E31" s="12" t="n"/>
       <c r="F31" s="5" t="n"/>
       <c r="G31" s="5" t="n"/>
       <c r="H31" s="5" t="n"/>
       <c r="I31" s="5" t="n"/>
       <c r="J31" s="5" t="n"/>
-      <c r="K31" s="9" t="inlineStr"/>
+      <c r="K31" s="12" t="n"/>
       <c r="L31" s="5" t="n"/>
       <c r="M31" s="5" t="n"/>
       <c r="N31" s="5" t="n"/>
@@ -1164,7 +1212,7 @@
       <c r="P31" s="5" t="n"/>
       <c r="Q31" s="5" t="n"/>
       <c r="R31" s="5" t="n"/>
-      <c r="S31" s="9" t="inlineStr"/>
+      <c r="S31" s="12" t="n"/>
       <c r="T31" s="5" t="n"/>
       <c r="U31" s="5" t="n"/>
       <c r="V31" s="5" t="n"/>
@@ -1172,17 +1220,17 @@
       <c r="X31" s="5" t="n"/>
     </row>
     <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="9" t="inlineStr"/>
+      <c r="A32" s="11" t="n"/>
       <c r="B32" s="5" t="n"/>
       <c r="C32" s="5" t="n"/>
       <c r="D32" s="5" t="n"/>
-      <c r="E32" s="9" t="inlineStr"/>
+      <c r="E32" s="12" t="n"/>
       <c r="F32" s="5" t="n"/>
       <c r="G32" s="5" t="n"/>
       <c r="H32" s="5" t="n"/>
       <c r="I32" s="5" t="n"/>
       <c r="J32" s="5" t="n"/>
-      <c r="K32" s="9" t="inlineStr"/>
+      <c r="K32" s="12" t="n"/>
       <c r="L32" s="5" t="n"/>
       <c r="M32" s="5" t="n"/>
       <c r="N32" s="5" t="n"/>
@@ -1190,7 +1238,7 @@
       <c r="P32" s="5" t="n"/>
       <c r="Q32" s="5" t="n"/>
       <c r="R32" s="5" t="n"/>
-      <c r="S32" s="9" t="inlineStr"/>
+      <c r="S32" s="12" t="n"/>
       <c r="T32" s="5" t="n"/>
       <c r="U32" s="5" t="n"/>
       <c r="V32" s="5" t="n"/>
@@ -1198,17 +1246,17 @@
       <c r="X32" s="5" t="n"/>
     </row>
     <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="9" t="inlineStr"/>
+      <c r="A33" s="11" t="n"/>
       <c r="B33" s="5" t="n"/>
       <c r="C33" s="5" t="n"/>
       <c r="D33" s="5" t="n"/>
-      <c r="E33" s="9" t="inlineStr"/>
+      <c r="E33" s="12" t="n"/>
       <c r="F33" s="5" t="n"/>
       <c r="G33" s="5" t="n"/>
       <c r="H33" s="5" t="n"/>
       <c r="I33" s="5" t="n"/>
       <c r="J33" s="5" t="n"/>
-      <c r="K33" s="9" t="inlineStr"/>
+      <c r="K33" s="12" t="n"/>
       <c r="L33" s="5" t="n"/>
       <c r="M33" s="5" t="n"/>
       <c r="N33" s="5" t="n"/>
@@ -1216,7 +1264,7 @@
       <c r="P33" s="5" t="n"/>
       <c r="Q33" s="5" t="n"/>
       <c r="R33" s="5" t="n"/>
-      <c r="S33" s="9" t="inlineStr"/>
+      <c r="S33" s="12" t="n"/>
       <c r="T33" s="5" t="n"/>
       <c r="U33" s="5" t="n"/>
       <c r="V33" s="5" t="n"/>
@@ -1224,17 +1272,17 @@
       <c r="X33" s="5" t="n"/>
     </row>
     <row r="34" ht="22" customHeight="1">
-      <c r="A34" s="9" t="inlineStr"/>
+      <c r="A34" s="11" t="n"/>
       <c r="B34" s="5" t="n"/>
       <c r="C34" s="5" t="n"/>
       <c r="D34" s="5" t="n"/>
-      <c r="E34" s="9" t="inlineStr"/>
+      <c r="E34" s="12" t="n"/>
       <c r="F34" s="5" t="n"/>
       <c r="G34" s="5" t="n"/>
       <c r="H34" s="5" t="n"/>
       <c r="I34" s="5" t="n"/>
       <c r="J34" s="5" t="n"/>
-      <c r="K34" s="9" t="inlineStr"/>
+      <c r="K34" s="12" t="n"/>
       <c r="L34" s="5" t="n"/>
       <c r="M34" s="5" t="n"/>
       <c r="N34" s="5" t="n"/>
@@ -1242,51 +1290,30 @@
       <c r="P34" s="5" t="n"/>
       <c r="Q34" s="5" t="n"/>
       <c r="R34" s="5" t="n"/>
-      <c r="S34" s="9" t="inlineStr"/>
+      <c r="S34" s="12" t="n"/>
       <c r="T34" s="5" t="n"/>
       <c r="U34" s="5" t="n"/>
       <c r="V34" s="5" t="n"/>
       <c r="W34" s="5" t="n"/>
       <c r="X34" s="5" t="n"/>
     </row>
-    <row r="35" ht="22" customHeight="1">
-      <c r="A35" s="9" t="inlineStr"/>
-      <c r="B35" s="5" t="n"/>
-      <c r="C35" s="5" t="n"/>
-      <c r="D35" s="5" t="n"/>
-      <c r="E35" s="9" t="inlineStr"/>
-      <c r="F35" s="5" t="n"/>
-      <c r="G35" s="5" t="n"/>
-      <c r="H35" s="5" t="n"/>
-      <c r="I35" s="5" t="n"/>
-      <c r="J35" s="5" t="n"/>
-      <c r="K35" s="9" t="inlineStr"/>
-      <c r="L35" s="5" t="n"/>
-      <c r="M35" s="5" t="n"/>
-      <c r="N35" s="5" t="n"/>
-      <c r="O35" s="5" t="n"/>
-      <c r="P35" s="5" t="n"/>
-      <c r="Q35" s="5" t="n"/>
-      <c r="R35" s="5" t="n"/>
-      <c r="S35" s="9" t="inlineStr"/>
-      <c r="T35" s="5" t="n"/>
-      <c r="U35" s="5" t="n"/>
-      <c r="V35" s="5" t="n"/>
-      <c r="W35" s="5" t="n"/>
-      <c r="X35" s="5" t="n"/>
-    </row>
-    <row r="36" ht="22" customHeight="1">
-      <c r="A36" s="9" t="inlineStr"/>
+    <row r="35" ht="6" customHeight="1"/>
+    <row r="36" ht="34" customHeight="1">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  최초 신고 담당(119)</t>
+        </is>
+      </c>
       <c r="B36" s="5" t="n"/>
       <c r="C36" s="5" t="n"/>
       <c r="D36" s="5" t="n"/>
-      <c r="E36" s="9" t="inlineStr"/>
+      <c r="E36" s="5" t="n"/>
       <c r="F36" s="5" t="n"/>
-      <c r="G36" s="5" t="n"/>
+      <c r="G36" s="6" t="n"/>
       <c r="H36" s="5" t="n"/>
       <c r="I36" s="5" t="n"/>
       <c r="J36" s="5" t="n"/>
-      <c r="K36" s="9" t="inlineStr"/>
+      <c r="K36" s="5" t="n"/>
       <c r="L36" s="5" t="n"/>
       <c r="M36" s="5" t="n"/>
       <c r="N36" s="5" t="n"/>
@@ -1294,25 +1321,29 @@
       <c r="P36" s="5" t="n"/>
       <c r="Q36" s="5" t="n"/>
       <c r="R36" s="5" t="n"/>
-      <c r="S36" s="9" t="inlineStr"/>
+      <c r="S36" s="5" t="n"/>
       <c r="T36" s="5" t="n"/>
       <c r="U36" s="5" t="n"/>
       <c r="V36" s="5" t="n"/>
       <c r="W36" s="5" t="n"/>
       <c r="X36" s="5" t="n"/>
     </row>
-    <row r="37" ht="22" customHeight="1">
-      <c r="A37" s="9" t="inlineStr"/>
+    <row r="37" ht="24" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  현장 지휘</t>
+        </is>
+      </c>
       <c r="B37" s="5" t="n"/>
       <c r="C37" s="5" t="n"/>
       <c r="D37" s="5" t="n"/>
-      <c r="E37" s="9" t="inlineStr"/>
+      <c r="E37" s="5" t="n"/>
       <c r="F37" s="5" t="n"/>
-      <c r="G37" s="5" t="n"/>
+      <c r="G37" s="6" t="n"/>
       <c r="H37" s="5" t="n"/>
       <c r="I37" s="5" t="n"/>
       <c r="J37" s="5" t="n"/>
-      <c r="K37" s="9" t="inlineStr"/>
+      <c r="K37" s="5" t="n"/>
       <c r="L37" s="5" t="n"/>
       <c r="M37" s="5" t="n"/>
       <c r="N37" s="5" t="n"/>
@@ -1320,147 +1351,97 @@
       <c r="P37" s="5" t="n"/>
       <c r="Q37" s="5" t="n"/>
       <c r="R37" s="5" t="n"/>
-      <c r="S37" s="9" t="inlineStr"/>
+      <c r="S37" s="5" t="n"/>
       <c r="T37" s="5" t="n"/>
       <c r="U37" s="5" t="n"/>
       <c r="V37" s="5" t="n"/>
       <c r="W37" s="5" t="n"/>
       <c r="X37" s="5" t="n"/>
     </row>
-    <row r="38" ht="6" customHeight="1"/>
-    <row r="39" ht="24" customHeight="1">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  최초 신고 담당(119)</t>
-        </is>
-      </c>
-      <c r="B39" s="5" t="n"/>
-      <c r="C39" s="5" t="n"/>
-      <c r="D39" s="5" t="n"/>
-      <c r="E39" s="5" t="n"/>
-      <c r="F39" s="5" t="n"/>
-      <c r="G39" s="6" t="inlineStr"/>
-      <c r="H39" s="5" t="n"/>
-      <c r="I39" s="5" t="n"/>
-      <c r="J39" s="5" t="n"/>
-      <c r="K39" s="5" t="n"/>
-      <c r="L39" s="5" t="n"/>
-      <c r="M39" s="5" t="n"/>
-      <c r="N39" s="5" t="n"/>
-      <c r="O39" s="5" t="n"/>
-      <c r="P39" s="5" t="n"/>
-      <c r="Q39" s="5" t="n"/>
-      <c r="R39" s="5" t="n"/>
-      <c r="S39" s="5" t="n"/>
-      <c r="T39" s="5" t="n"/>
-      <c r="U39" s="5" t="n"/>
-      <c r="V39" s="5" t="n"/>
-      <c r="W39" s="5" t="n"/>
-      <c r="X39" s="5" t="n"/>
-    </row>
-    <row r="40" ht="24" customHeight="1">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  현장 지휘</t>
-        </is>
-      </c>
-      <c r="B40" s="5" t="n"/>
-      <c r="C40" s="5" t="n"/>
-      <c r="D40" s="5" t="n"/>
-      <c r="E40" s="5" t="n"/>
-      <c r="F40" s="5" t="n"/>
-      <c r="G40" s="6" t="inlineStr"/>
-      <c r="H40" s="5" t="n"/>
-      <c r="I40" s="5" t="n"/>
-      <c r="J40" s="5" t="n"/>
-      <c r="K40" s="5" t="n"/>
-      <c r="L40" s="5" t="n"/>
-      <c r="M40" s="5" t="n"/>
-      <c r="N40" s="5" t="n"/>
-      <c r="O40" s="5" t="n"/>
-      <c r="P40" s="5" t="n"/>
-      <c r="Q40" s="5" t="n"/>
-      <c r="R40" s="5" t="n"/>
-      <c r="S40" s="5" t="n"/>
-      <c r="T40" s="5" t="n"/>
-      <c r="U40" s="5" t="n"/>
-      <c r="V40" s="5" t="n"/>
-      <c r="W40" s="5" t="n"/>
-      <c r="X40" s="5" t="n"/>
-    </row>
-    <row r="41" ht="24" customHeight="1">
-      <c r="A41" s="4" t="inlineStr">
+    <row r="38" ht="24" customHeight="1">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  발주처·감리 연락</t>
         </is>
       </c>
-      <c r="B41" s="5" t="n"/>
-      <c r="C41" s="5" t="n"/>
-      <c r="D41" s="5" t="n"/>
-      <c r="E41" s="5" t="n"/>
-      <c r="F41" s="5" t="n"/>
-      <c r="G41" s="6" t="inlineStr"/>
-      <c r="H41" s="5" t="n"/>
-      <c r="I41" s="5" t="n"/>
-      <c r="J41" s="5" t="n"/>
-      <c r="K41" s="5" t="n"/>
-      <c r="L41" s="5" t="n"/>
-      <c r="M41" s="5" t="n"/>
-      <c r="N41" s="5" t="n"/>
-      <c r="O41" s="5" t="n"/>
-      <c r="P41" s="5" t="n"/>
-      <c r="Q41" s="5" t="n"/>
-      <c r="R41" s="5" t="n"/>
-      <c r="S41" s="5" t="n"/>
-      <c r="T41" s="5" t="n"/>
-      <c r="U41" s="5" t="n"/>
-      <c r="V41" s="5" t="n"/>
-      <c r="W41" s="5" t="n"/>
-      <c r="X41" s="5" t="n"/>
-    </row>
-    <row r="42" ht="6" customHeight="1"/>
-    <row r="43" ht="10" customHeight="1"/>
-    <row r="44" ht="26" customHeight="1">
-      <c r="A44" s="10" t="inlineStr">
-        <is>
-          <t>년        월        일</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="K45" s="11" t="inlineStr">
+      <c r="B38" s="5" t="n"/>
+      <c r="C38" s="5" t="n"/>
+      <c r="D38" s="5" t="n"/>
+      <c r="E38" s="5" t="n"/>
+      <c r="F38" s="5" t="n"/>
+      <c r="G38" s="6" t="n"/>
+      <c r="H38" s="5" t="n"/>
+      <c r="I38" s="5" t="n"/>
+      <c r="J38" s="5" t="n"/>
+      <c r="K38" s="5" t="n"/>
+      <c r="L38" s="5" t="n"/>
+      <c r="M38" s="5" t="n"/>
+      <c r="N38" s="5" t="n"/>
+      <c r="O38" s="5" t="n"/>
+      <c r="P38" s="5" t="n"/>
+      <c r="Q38" s="5" t="n"/>
+      <c r="R38" s="5" t="n"/>
+      <c r="S38" s="5" t="n"/>
+      <c r="T38" s="5" t="n"/>
+      <c r="U38" s="5" t="n"/>
+      <c r="V38" s="5" t="n"/>
+      <c r="W38" s="5" t="n"/>
+      <c r="X38" s="5" t="n"/>
+    </row>
+    <row r="39" ht="6" customHeight="1"/>
+    <row r="40" ht="10" customHeight="1"/>
+    <row r="41" ht="26" customHeight="1">
+      <c r="A41" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          년        월        일</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="24" customHeight="1">
+      <c r="A42" s="14" t="inlineStr"/>
+      <c r="K42" s="15" t="inlineStr">
         <is>
           <t>현장대리인</t>
         </is>
       </c>
-      <c r="S45" s="10" t="inlineStr">
+      <c r="Q42" s="16" t="n"/>
+      <c r="U42" s="17" t="inlineStr">
         <is>
           <t>(서명 또는 인)</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="K46" s="11" t="inlineStr">
+    <row r="43" ht="24" customHeight="1">
+      <c r="A43" s="14" t="inlineStr"/>
+      <c r="K43" s="15" t="inlineStr">
         <is>
           <t>안전관리자</t>
         </is>
       </c>
-      <c r="S46" s="10" t="inlineStr">
+      <c r="Q43" s="16" t="n"/>
+      <c r="U43" s="17" t="inlineStr">
         <is>
           <t>(서명 또는 인)</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="6" customHeight="1"/>
-    <row r="50">
-      <c r="A50" s="12" t="inlineStr">
-        <is>
-          <t>발주기관이 정한 서식이 있으면 그 서식을 사용하세요. 이 줄과 1행은 인쇄 전에 지우셔도 됩니다.</t>
+    <row r="44" ht="6" customHeight="1"/>
+    <row r="46" ht="34" customHeight="1">
+      <c r="A46" s="18" t="inlineStr">
+        <is>
+          <t>노란 칸 = 요율·기준값(발주기관 기준으로 고쳐 씀) · 옅은 하늘색 칸 = 자동 계산(지우지 마세요) · 뒤 시트에 «작성 예시» 가 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="19.5" customHeight="1">
+      <c r="A47" s="18" t="inlineStr">
+        <is>
+          <t>발주기관이 정한 서식이 있으면 그 서식을 쓰세요. 이 줄과 1행은 지워도 됩니다.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="126">
+  <mergeCells count="118">
     <mergeCell ref="I14:L14"/>
     <mergeCell ref="M18:S18"/>
     <mergeCell ref="T15:X15"/>
@@ -1470,125 +1451,1333 @@
     <mergeCell ref="M17:S17"/>
     <mergeCell ref="A29:D29"/>
     <mergeCell ref="S28:X28"/>
-    <mergeCell ref="K36:R36"/>
+    <mergeCell ref="A43:J43"/>
     <mergeCell ref="E30:J30"/>
     <mergeCell ref="A13:D13"/>
-    <mergeCell ref="K45:R45"/>
     <mergeCell ref="A3:X3"/>
     <mergeCell ref="M19:S19"/>
     <mergeCell ref="A31:D31"/>
     <mergeCell ref="K29:R29"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="A15:D15"/>
-    <mergeCell ref="S45:X45"/>
     <mergeCell ref="K31:R31"/>
     <mergeCell ref="S29:X29"/>
+    <mergeCell ref="A38:F38"/>
     <mergeCell ref="E32:J32"/>
     <mergeCell ref="I16:L16"/>
     <mergeCell ref="S31:X31"/>
-    <mergeCell ref="A40:F40"/>
     <mergeCell ref="A16:D16"/>
     <mergeCell ref="T22:X22"/>
     <mergeCell ref="A27:D27"/>
     <mergeCell ref="I18:L18"/>
+    <mergeCell ref="A24:X24"/>
     <mergeCell ref="M13:S13"/>
     <mergeCell ref="M21:S21"/>
     <mergeCell ref="A33:D33"/>
     <mergeCell ref="A7:F7"/>
-    <mergeCell ref="A41:F41"/>
+    <mergeCell ref="U42:X42"/>
     <mergeCell ref="A17:D17"/>
     <mergeCell ref="G7:X7"/>
     <mergeCell ref="A22:D22"/>
-    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="G38:X38"/>
     <mergeCell ref="T20:X20"/>
     <mergeCell ref="T14:X14"/>
-    <mergeCell ref="A25:X25"/>
+    <mergeCell ref="K33:R33"/>
     <mergeCell ref="I20:L20"/>
-    <mergeCell ref="K33:R33"/>
     <mergeCell ref="A19:D19"/>
     <mergeCell ref="E34:J34"/>
     <mergeCell ref="A28:D28"/>
     <mergeCell ref="E22:H22"/>
     <mergeCell ref="I13:L13"/>
     <mergeCell ref="S34:X34"/>
-    <mergeCell ref="K35:R35"/>
-    <mergeCell ref="A50:X50"/>
-    <mergeCell ref="E36:J36"/>
     <mergeCell ref="A30:D30"/>
     <mergeCell ref="E21:H21"/>
     <mergeCell ref="I15:L15"/>
-    <mergeCell ref="S36:X36"/>
+    <mergeCell ref="A47:X47"/>
     <mergeCell ref="S30:X30"/>
     <mergeCell ref="E14:H14"/>
-    <mergeCell ref="E23:H23"/>
     <mergeCell ref="A9:F9"/>
-    <mergeCell ref="E37:J37"/>
     <mergeCell ref="G9:X9"/>
-    <mergeCell ref="A44:X44"/>
     <mergeCell ref="T17:X17"/>
-    <mergeCell ref="S46:X46"/>
+    <mergeCell ref="A26:D26"/>
     <mergeCell ref="T19:X19"/>
     <mergeCell ref="M15:S15"/>
-    <mergeCell ref="G39:X39"/>
+    <mergeCell ref="U43:X43"/>
+    <mergeCell ref="A42:J42"/>
     <mergeCell ref="I17:L17"/>
+    <mergeCell ref="G37:X37"/>
     <mergeCell ref="E16:H16"/>
+    <mergeCell ref="A41:X41"/>
     <mergeCell ref="I19:L19"/>
-    <mergeCell ref="M23:S23"/>
+    <mergeCell ref="K43:P43"/>
     <mergeCell ref="E18:H18"/>
+    <mergeCell ref="K26:R26"/>
     <mergeCell ref="A34:D34"/>
     <mergeCell ref="S33:X33"/>
+    <mergeCell ref="K42:P42"/>
     <mergeCell ref="E27:J27"/>
     <mergeCell ref="A8:F8"/>
-    <mergeCell ref="A36:D36"/>
-    <mergeCell ref="S35:X35"/>
+    <mergeCell ref="Q42:T42"/>
     <mergeCell ref="T21:X21"/>
-    <mergeCell ref="G41:X41"/>
     <mergeCell ref="E20:H20"/>
     <mergeCell ref="K27:R27"/>
     <mergeCell ref="M20:S20"/>
-    <mergeCell ref="T23:X23"/>
-    <mergeCell ref="A39:F39"/>
     <mergeCell ref="E13:H13"/>
     <mergeCell ref="T13:X13"/>
-    <mergeCell ref="A37:D37"/>
     <mergeCell ref="T16:X16"/>
+    <mergeCell ref="A36:F36"/>
     <mergeCell ref="I21:L21"/>
     <mergeCell ref="M22:S22"/>
     <mergeCell ref="A21:D21"/>
+    <mergeCell ref="G36:X36"/>
     <mergeCell ref="A11:X11"/>
     <mergeCell ref="E15:H15"/>
     <mergeCell ref="K28:R28"/>
     <mergeCell ref="T18:X18"/>
     <mergeCell ref="A32:D32"/>
-    <mergeCell ref="K37:R37"/>
     <mergeCell ref="A14:D14"/>
-    <mergeCell ref="I23:L23"/>
     <mergeCell ref="E29:J29"/>
-    <mergeCell ref="A23:D23"/>
     <mergeCell ref="K30:R30"/>
-    <mergeCell ref="S37:X37"/>
+    <mergeCell ref="A37:F37"/>
     <mergeCell ref="E31:J31"/>
     <mergeCell ref="G6:X6"/>
+    <mergeCell ref="A46:X46"/>
     <mergeCell ref="M14:S14"/>
     <mergeCell ref="G5:X5"/>
+    <mergeCell ref="Q43:T43"/>
     <mergeCell ref="K32:R32"/>
-    <mergeCell ref="K46:R46"/>
+    <mergeCell ref="E26:J26"/>
     <mergeCell ref="E17:H17"/>
     <mergeCell ref="S32:X32"/>
-    <mergeCell ref="G40:X40"/>
+    <mergeCell ref="S26:X26"/>
     <mergeCell ref="E19:H19"/>
     <mergeCell ref="I22:L22"/>
     <mergeCell ref="A18:D18"/>
     <mergeCell ref="E33:J33"/>
     <mergeCell ref="A1:L1"/>
+    <mergeCell ref="S27:X27"/>
     <mergeCell ref="M16:S16"/>
-    <mergeCell ref="S27:X27"/>
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="M1:X1"/>
-    <mergeCell ref="E35:J35"/>
     <mergeCell ref="G8:X8"/>
   </mergeCells>
-  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00F59E0B"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:X46"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3.6" customWidth="1" min="1" max="1"/>
+    <col width="3.6" customWidth="1" min="2" max="2"/>
+    <col width="3.6" customWidth="1" min="3" max="3"/>
+    <col width="3.6" customWidth="1" min="4" max="4"/>
+    <col width="3.6" customWidth="1" min="5" max="5"/>
+    <col width="3.6" customWidth="1" min="6" max="6"/>
+    <col width="3.6" customWidth="1" min="7" max="7"/>
+    <col width="3.6" customWidth="1" min="8" max="8"/>
+    <col width="3.6" customWidth="1" min="9" max="9"/>
+    <col width="3.6" customWidth="1" min="10" max="10"/>
+    <col width="3.6" customWidth="1" min="11" max="11"/>
+    <col width="3.6" customWidth="1" min="12" max="12"/>
+    <col width="3.6" customWidth="1" min="13" max="13"/>
+    <col width="3.6" customWidth="1" min="14" max="14"/>
+    <col width="3.6" customWidth="1" min="15" max="15"/>
+    <col width="3.6" customWidth="1" min="16" max="16"/>
+    <col width="3.6" customWidth="1" min="17" max="17"/>
+    <col width="3.6" customWidth="1" min="18" max="18"/>
+    <col width="3.6" customWidth="1" min="19" max="19"/>
+    <col width="3.6" customWidth="1" min="20" max="20"/>
+    <col width="3.6" customWidth="1" min="21" max="21"/>
+    <col width="3.6" customWidth="1" min="22" max="22"/>
+    <col width="3.6" customWidth="1" min="23" max="23"/>
+    <col width="3.6" customWidth="1" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+        </is>
+      </c>
+      <c r="M1" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">작성 예시 (가상의 현장)  </t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="6" customHeight="1"/>
+    <row r="3" ht="38" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>현 장  조 직 도  ·  비 상  조 직 도</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="10" customHeight="1"/>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  공 사 명</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>가나지구 배수로 정비공사</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="5" t="n"/>
+      <c r="J5" s="5" t="n"/>
+      <c r="K5" s="5" t="n"/>
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="5" t="n"/>
+      <c r="N5" s="5" t="n"/>
+      <c r="O5" s="5" t="n"/>
+      <c r="P5" s="5" t="n"/>
+      <c r="Q5" s="5" t="n"/>
+      <c r="R5" s="5" t="n"/>
+      <c r="S5" s="5" t="n"/>
+      <c r="T5" s="5" t="n"/>
+      <c r="U5" s="5" t="n"/>
+      <c r="V5" s="5" t="n"/>
+      <c r="W5" s="5" t="n"/>
+      <c r="X5" s="5" t="n"/>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  발 주 기 관</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>가나시 건설과</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="n"/>
+      <c r="I6" s="5" t="n"/>
+      <c r="J6" s="5" t="n"/>
+      <c r="K6" s="5" t="n"/>
+      <c r="L6" s="5" t="n"/>
+      <c r="M6" s="5" t="n"/>
+      <c r="N6" s="5" t="n"/>
+      <c r="O6" s="5" t="n"/>
+      <c r="P6" s="5" t="n"/>
+      <c r="Q6" s="5" t="n"/>
+      <c r="R6" s="5" t="n"/>
+      <c r="S6" s="5" t="n"/>
+      <c r="T6" s="5" t="n"/>
+      <c r="U6" s="5" t="n"/>
+      <c r="V6" s="5" t="n"/>
+      <c r="W6" s="5" t="n"/>
+      <c r="X6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  계 약 금 액</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="7" t="n">
+        <v>963241000</v>
+      </c>
+      <c r="H7" s="5" t="n"/>
+      <c r="I7" s="5" t="n"/>
+      <c r="J7" s="5" t="n"/>
+      <c r="K7" s="5" t="n"/>
+      <c r="L7" s="5" t="n"/>
+      <c r="M7" s="5" t="n"/>
+      <c r="N7" s="5" t="n"/>
+      <c r="O7" s="5" t="n"/>
+      <c r="P7" s="5" t="n"/>
+      <c r="Q7" s="5" t="n"/>
+      <c r="R7" s="5" t="n"/>
+      <c r="S7" s="5" t="n"/>
+      <c r="T7" s="5" t="n"/>
+      <c r="U7" s="5" t="n"/>
+      <c r="V7" s="5" t="n"/>
+      <c r="W7" s="5" t="n"/>
+      <c r="X7" s="5" t="n"/>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  공        기</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>2026. 3. 9. ~ 2026. 12. 31. (298일)</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="n"/>
+      <c r="I8" s="5" t="n"/>
+      <c r="J8" s="5" t="n"/>
+      <c r="K8" s="5" t="n"/>
+      <c r="L8" s="5" t="n"/>
+      <c r="M8" s="5" t="n"/>
+      <c r="N8" s="5" t="n"/>
+      <c r="O8" s="5" t="n"/>
+      <c r="P8" s="5" t="n"/>
+      <c r="Q8" s="5" t="n"/>
+      <c r="R8" s="5" t="n"/>
+      <c r="S8" s="5" t="n"/>
+      <c r="T8" s="5" t="n"/>
+      <c r="U8" s="5" t="n"/>
+      <c r="V8" s="5" t="n"/>
+      <c r="W8" s="5" t="n"/>
+      <c r="X8" s="5" t="n"/>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  작 성 일 자</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="8" t="n">
+        <v>46294</v>
+      </c>
+      <c r="H9" s="5" t="n"/>
+      <c r="I9" s="5" t="n"/>
+      <c r="J9" s="5" t="n"/>
+      <c r="K9" s="5" t="n"/>
+      <c r="L9" s="5" t="n"/>
+      <c r="M9" s="5" t="n"/>
+      <c r="N9" s="5" t="n"/>
+      <c r="O9" s="5" t="n"/>
+      <c r="P9" s="5" t="n"/>
+      <c r="Q9" s="5" t="n"/>
+      <c r="R9" s="5" t="n"/>
+      <c r="S9" s="5" t="n"/>
+      <c r="T9" s="5" t="n"/>
+      <c r="U9" s="5" t="n"/>
+      <c r="V9" s="5" t="n"/>
+      <c r="W9" s="5" t="n"/>
+      <c r="X9" s="5" t="n"/>
+    </row>
+    <row r="10" ht="6" customHeight="1"/>
+    <row r="11" ht="26" customHeight="1">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>■ 평상시 조직</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="6" customHeight="1"/>
+    <row r="13" ht="24" customHeight="1">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>직책</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5" t="n"/>
+      <c r="H13" s="5" t="n"/>
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>성명</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="n"/>
+      <c r="K13" s="5" t="n"/>
+      <c r="L13" s="5" t="n"/>
+      <c r="M13" s="10" t="inlineStr">
+        <is>
+          <t>담당 업무</t>
+        </is>
+      </c>
+      <c r="N13" s="5" t="n"/>
+      <c r="O13" s="5" t="n"/>
+      <c r="P13" s="5" t="n"/>
+      <c r="Q13" s="5" t="n"/>
+      <c r="R13" s="5" t="n"/>
+      <c r="S13" s="5" t="n"/>
+      <c r="T13" s="10" t="inlineStr">
+        <is>
+          <t>연락처</t>
+        </is>
+      </c>
+      <c r="U13" s="5" t="n"/>
+      <c r="V13" s="5" t="n"/>
+      <c r="W13" s="5" t="n"/>
+      <c r="X13" s="5" t="n"/>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>총괄</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>현장대리인</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="5" t="n"/>
+      <c r="I14" s="11" t="inlineStr">
+        <is>
+          <t>김철수</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="n"/>
+      <c r="K14" s="5" t="n"/>
+      <c r="L14" s="5" t="n"/>
+      <c r="M14" s="12" t="inlineStr">
+        <is>
+          <t>현장 총괄</t>
+        </is>
+      </c>
+      <c r="N14" s="5" t="n"/>
+      <c r="O14" s="5" t="n"/>
+      <c r="P14" s="5" t="n"/>
+      <c r="Q14" s="5" t="n"/>
+      <c r="R14" s="5" t="n"/>
+      <c r="S14" s="5" t="n"/>
+      <c r="T14" s="11" t="inlineStr">
+        <is>
+          <t>000-0000-0000</t>
+        </is>
+      </c>
+      <c r="U14" s="5" t="n"/>
+      <c r="V14" s="5" t="n"/>
+      <c r="W14" s="5" t="n"/>
+      <c r="X14" s="5" t="n"/>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>공사</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>공사과장</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="5" t="n"/>
+      <c r="I15" s="11" t="inlineStr">
+        <is>
+          <t>이감독</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="n"/>
+      <c r="K15" s="5" t="n"/>
+      <c r="L15" s="5" t="n"/>
+      <c r="M15" s="12" t="inlineStr">
+        <is>
+          <t>작업 지휘</t>
+        </is>
+      </c>
+      <c r="N15" s="5" t="n"/>
+      <c r="O15" s="5" t="n"/>
+      <c r="P15" s="5" t="n"/>
+      <c r="Q15" s="5" t="n"/>
+      <c r="R15" s="5" t="n"/>
+      <c r="S15" s="5" t="n"/>
+      <c r="T15" s="11" t="inlineStr">
+        <is>
+          <t>000-0000-0000</t>
+        </is>
+      </c>
+      <c r="U15" s="5" t="n"/>
+      <c r="V15" s="5" t="n"/>
+      <c r="W15" s="5" t="n"/>
+      <c r="X15" s="5" t="n"/>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>안전</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>안전관리자</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="5" t="n"/>
+      <c r="H16" s="5" t="n"/>
+      <c r="I16" s="11" t="inlineStr">
+        <is>
+          <t>정안전</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="n"/>
+      <c r="K16" s="5" t="n"/>
+      <c r="L16" s="5" t="n"/>
+      <c r="M16" s="12" t="inlineStr">
+        <is>
+          <t>안전 점검·교육</t>
+        </is>
+      </c>
+      <c r="N16" s="5" t="n"/>
+      <c r="O16" s="5" t="n"/>
+      <c r="P16" s="5" t="n"/>
+      <c r="Q16" s="5" t="n"/>
+      <c r="R16" s="5" t="n"/>
+      <c r="S16" s="5" t="n"/>
+      <c r="T16" s="11" t="inlineStr">
+        <is>
+          <t>000-0000-0000</t>
+        </is>
+      </c>
+      <c r="U16" s="5" t="n"/>
+      <c r="V16" s="5" t="n"/>
+      <c r="W16" s="5" t="n"/>
+      <c r="X16" s="5" t="n"/>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>품질</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="11" t="inlineStr">
+        <is>
+          <t>품질관리자</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="5" t="n"/>
+      <c r="I17" s="11" t="inlineStr">
+        <is>
+          <t>한품질</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="n"/>
+      <c r="K17" s="5" t="n"/>
+      <c r="L17" s="5" t="n"/>
+      <c r="M17" s="12" t="inlineStr">
+        <is>
+          <t>시험·검사</t>
+        </is>
+      </c>
+      <c r="N17" s="5" t="n"/>
+      <c r="O17" s="5" t="n"/>
+      <c r="P17" s="5" t="n"/>
+      <c r="Q17" s="5" t="n"/>
+      <c r="R17" s="5" t="n"/>
+      <c r="S17" s="5" t="n"/>
+      <c r="T17" s="11" t="inlineStr">
+        <is>
+          <t>000-0000-0000</t>
+        </is>
+      </c>
+      <c r="U17" s="5" t="n"/>
+      <c r="V17" s="5" t="n"/>
+      <c r="W17" s="5" t="n"/>
+      <c r="X17" s="5" t="n"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>공무</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t>공무</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="5" t="n"/>
+      <c r="H18" s="5" t="n"/>
+      <c r="I18" s="11" t="inlineStr">
+        <is>
+          <t>오공무</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="n"/>
+      <c r="K18" s="5" t="n"/>
+      <c r="L18" s="5" t="n"/>
+      <c r="M18" s="12" t="inlineStr">
+        <is>
+          <t>서류·기성</t>
+        </is>
+      </c>
+      <c r="N18" s="5" t="n"/>
+      <c r="O18" s="5" t="n"/>
+      <c r="P18" s="5" t="n"/>
+      <c r="Q18" s="5" t="n"/>
+      <c r="R18" s="5" t="n"/>
+      <c r="S18" s="5" t="n"/>
+      <c r="T18" s="11" t="inlineStr">
+        <is>
+          <t>000-0000-0000</t>
+        </is>
+      </c>
+      <c r="U18" s="5" t="n"/>
+      <c r="V18" s="5" t="n"/>
+      <c r="W18" s="5" t="n"/>
+      <c r="X18" s="5" t="n"/>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="11" t="n"/>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="11" t="n"/>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5" t="n"/>
+      <c r="H19" s="5" t="n"/>
+      <c r="I19" s="11" t="n"/>
+      <c r="J19" s="5" t="n"/>
+      <c r="K19" s="5" t="n"/>
+      <c r="L19" s="5" t="n"/>
+      <c r="M19" s="12" t="n"/>
+      <c r="N19" s="5" t="n"/>
+      <c r="O19" s="5" t="n"/>
+      <c r="P19" s="5" t="n"/>
+      <c r="Q19" s="5" t="n"/>
+      <c r="R19" s="5" t="n"/>
+      <c r="S19" s="5" t="n"/>
+      <c r="T19" s="11" t="n"/>
+      <c r="U19" s="5" t="n"/>
+      <c r="V19" s="5" t="n"/>
+      <c r="W19" s="5" t="n"/>
+      <c r="X19" s="5" t="n"/>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="11" t="n"/>
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="11" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="5" t="n"/>
+      <c r="I20" s="11" t="n"/>
+      <c r="J20" s="5" t="n"/>
+      <c r="K20" s="5" t="n"/>
+      <c r="L20" s="5" t="n"/>
+      <c r="M20" s="12" t="n"/>
+      <c r="N20" s="5" t="n"/>
+      <c r="O20" s="5" t="n"/>
+      <c r="P20" s="5" t="n"/>
+      <c r="Q20" s="5" t="n"/>
+      <c r="R20" s="5" t="n"/>
+      <c r="S20" s="5" t="n"/>
+      <c r="T20" s="11" t="n"/>
+      <c r="U20" s="5" t="n"/>
+      <c r="V20" s="5" t="n"/>
+      <c r="W20" s="5" t="n"/>
+      <c r="X20" s="5" t="n"/>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="11" t="n"/>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="11" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="5" t="n"/>
+      <c r="I21" s="11" t="n"/>
+      <c r="J21" s="5" t="n"/>
+      <c r="K21" s="5" t="n"/>
+      <c r="L21" s="5" t="n"/>
+      <c r="M21" s="12" t="n"/>
+      <c r="N21" s="5" t="n"/>
+      <c r="O21" s="5" t="n"/>
+      <c r="P21" s="5" t="n"/>
+      <c r="Q21" s="5" t="n"/>
+      <c r="R21" s="5" t="n"/>
+      <c r="S21" s="5" t="n"/>
+      <c r="T21" s="11" t="n"/>
+      <c r="U21" s="5" t="n"/>
+      <c r="V21" s="5" t="n"/>
+      <c r="W21" s="5" t="n"/>
+      <c r="X21" s="5" t="n"/>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="11" t="n"/>
+      <c r="B22" s="5" t="n"/>
+      <c r="C22" s="5" t="n"/>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="11" t="n"/>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="5" t="n"/>
+      <c r="I22" s="11" t="n"/>
+      <c r="J22" s="5" t="n"/>
+      <c r="K22" s="5" t="n"/>
+      <c r="L22" s="5" t="n"/>
+      <c r="M22" s="12" t="n"/>
+      <c r="N22" s="5" t="n"/>
+      <c r="O22" s="5" t="n"/>
+      <c r="P22" s="5" t="n"/>
+      <c r="Q22" s="5" t="n"/>
+      <c r="R22" s="5" t="n"/>
+      <c r="S22" s="5" t="n"/>
+      <c r="T22" s="11" t="n"/>
+      <c r="U22" s="5" t="n"/>
+      <c r="V22" s="5" t="n"/>
+      <c r="W22" s="5" t="n"/>
+      <c r="X22" s="5" t="n"/>
+    </row>
+    <row r="23" ht="6" customHeight="1"/>
+    <row r="24" ht="26" customHeight="1">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>■ 비상시 조직 (사고·재해 발생 시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="6" customHeight="1"/>
+    <row r="26" ht="24" customHeight="1">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="5" t="n"/>
+      <c r="D26" s="5" t="n"/>
+      <c r="E26" s="10" t="inlineStr">
+        <is>
+          <t>직책·성명</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="n"/>
+      <c r="G26" s="5" t="n"/>
+      <c r="H26" s="5" t="n"/>
+      <c r="I26" s="5" t="n"/>
+      <c r="J26" s="5" t="n"/>
+      <c r="K26" s="10" t="inlineStr">
+        <is>
+          <t>비상시 임무</t>
+        </is>
+      </c>
+      <c r="L26" s="5" t="n"/>
+      <c r="M26" s="5" t="n"/>
+      <c r="N26" s="5" t="n"/>
+      <c r="O26" s="5" t="n"/>
+      <c r="P26" s="5" t="n"/>
+      <c r="Q26" s="5" t="n"/>
+      <c r="R26" s="5" t="n"/>
+      <c r="S26" s="10" t="inlineStr">
+        <is>
+          <t>연락처</t>
+        </is>
+      </c>
+      <c r="T26" s="5" t="n"/>
+      <c r="U26" s="5" t="n"/>
+      <c r="V26" s="5" t="n"/>
+      <c r="W26" s="5" t="n"/>
+      <c r="X26" s="5" t="n"/>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t>지휘</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n"/>
+      <c r="C27" s="5" t="n"/>
+      <c r="D27" s="5" t="n"/>
+      <c r="E27" s="12" t="inlineStr">
+        <is>
+          <t>현장대리인 김철수</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="n"/>
+      <c r="G27" s="5" t="n"/>
+      <c r="H27" s="5" t="n"/>
+      <c r="I27" s="5" t="n"/>
+      <c r="J27" s="5" t="n"/>
+      <c r="K27" s="12" t="inlineStr">
+        <is>
+          <t>상황 지휘 · 작업 중지</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="n"/>
+      <c r="M27" s="5" t="n"/>
+      <c r="N27" s="5" t="n"/>
+      <c r="O27" s="5" t="n"/>
+      <c r="P27" s="5" t="n"/>
+      <c r="Q27" s="5" t="n"/>
+      <c r="R27" s="5" t="n"/>
+      <c r="S27" s="12" t="inlineStr">
+        <is>
+          <t>000-0000-0000</t>
+        </is>
+      </c>
+      <c r="T27" s="5" t="n"/>
+      <c r="U27" s="5" t="n"/>
+      <c r="V27" s="5" t="n"/>
+      <c r="W27" s="5" t="n"/>
+      <c r="X27" s="5" t="n"/>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t>신고</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n"/>
+      <c r="C28" s="5" t="n"/>
+      <c r="D28" s="5" t="n"/>
+      <c r="E28" s="12" t="inlineStr">
+        <is>
+          <t>안전관리자 정안전</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="n"/>
+      <c r="G28" s="5" t="n"/>
+      <c r="H28" s="5" t="n"/>
+      <c r="I28" s="5" t="n"/>
+      <c r="J28" s="5" t="n"/>
+      <c r="K28" s="12" t="inlineStr">
+        <is>
+          <t>119 신고 · 응급조치</t>
+        </is>
+      </c>
+      <c r="L28" s="5" t="n"/>
+      <c r="M28" s="5" t="n"/>
+      <c r="N28" s="5" t="n"/>
+      <c r="O28" s="5" t="n"/>
+      <c r="P28" s="5" t="n"/>
+      <c r="Q28" s="5" t="n"/>
+      <c r="R28" s="5" t="n"/>
+      <c r="S28" s="12" t="inlineStr">
+        <is>
+          <t>000-0000-0000</t>
+        </is>
+      </c>
+      <c r="T28" s="5" t="n"/>
+      <c r="U28" s="5" t="n"/>
+      <c r="V28" s="5" t="n"/>
+      <c r="W28" s="5" t="n"/>
+      <c r="X28" s="5" t="n"/>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>구조</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n"/>
+      <c r="C29" s="5" t="n"/>
+      <c r="D29" s="5" t="n"/>
+      <c r="E29" s="12" t="inlineStr">
+        <is>
+          <t>공사과장 이감독</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="n"/>
+      <c r="G29" s="5" t="n"/>
+      <c r="H29" s="5" t="n"/>
+      <c r="I29" s="5" t="n"/>
+      <c r="J29" s="5" t="n"/>
+      <c r="K29" s="12" t="inlineStr">
+        <is>
+          <t>구조 · 현장 통제</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="n"/>
+      <c r="M29" s="5" t="n"/>
+      <c r="N29" s="5" t="n"/>
+      <c r="O29" s="5" t="n"/>
+      <c r="P29" s="5" t="n"/>
+      <c r="Q29" s="5" t="n"/>
+      <c r="R29" s="5" t="n"/>
+      <c r="S29" s="12" t="inlineStr">
+        <is>
+          <t>000-0000-0000</t>
+        </is>
+      </c>
+      <c r="T29" s="5" t="n"/>
+      <c r="U29" s="5" t="n"/>
+      <c r="V29" s="5" t="n"/>
+      <c r="W29" s="5" t="n"/>
+      <c r="X29" s="5" t="n"/>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>연락</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n"/>
+      <c r="C30" s="5" t="n"/>
+      <c r="D30" s="5" t="n"/>
+      <c r="E30" s="12" t="inlineStr">
+        <is>
+          <t>공무 오공무</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="n"/>
+      <c r="G30" s="5" t="n"/>
+      <c r="H30" s="5" t="n"/>
+      <c r="I30" s="5" t="n"/>
+      <c r="J30" s="5" t="n"/>
+      <c r="K30" s="12" t="inlineStr">
+        <is>
+          <t>발주처·감리·본사 보고</t>
+        </is>
+      </c>
+      <c r="L30" s="5" t="n"/>
+      <c r="M30" s="5" t="n"/>
+      <c r="N30" s="5" t="n"/>
+      <c r="O30" s="5" t="n"/>
+      <c r="P30" s="5" t="n"/>
+      <c r="Q30" s="5" t="n"/>
+      <c r="R30" s="5" t="n"/>
+      <c r="S30" s="12" t="inlineStr">
+        <is>
+          <t>000-0000-0000</t>
+        </is>
+      </c>
+      <c r="T30" s="5" t="n"/>
+      <c r="U30" s="5" t="n"/>
+      <c r="V30" s="5" t="n"/>
+      <c r="W30" s="5" t="n"/>
+      <c r="X30" s="5" t="n"/>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="11" t="n"/>
+      <c r="B31" s="5" t="n"/>
+      <c r="C31" s="5" t="n"/>
+      <c r="D31" s="5" t="n"/>
+      <c r="E31" s="12" t="n"/>
+      <c r="F31" s="5" t="n"/>
+      <c r="G31" s="5" t="n"/>
+      <c r="H31" s="5" t="n"/>
+      <c r="I31" s="5" t="n"/>
+      <c r="J31" s="5" t="n"/>
+      <c r="K31" s="12" t="n"/>
+      <c r="L31" s="5" t="n"/>
+      <c r="M31" s="5" t="n"/>
+      <c r="N31" s="5" t="n"/>
+      <c r="O31" s="5" t="n"/>
+      <c r="P31" s="5" t="n"/>
+      <c r="Q31" s="5" t="n"/>
+      <c r="R31" s="5" t="n"/>
+      <c r="S31" s="12" t="n"/>
+      <c r="T31" s="5" t="n"/>
+      <c r="U31" s="5" t="n"/>
+      <c r="V31" s="5" t="n"/>
+      <c r="W31" s="5" t="n"/>
+      <c r="X31" s="5" t="n"/>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="11" t="n"/>
+      <c r="B32" s="5" t="n"/>
+      <c r="C32" s="5" t="n"/>
+      <c r="D32" s="5" t="n"/>
+      <c r="E32" s="12" t="n"/>
+      <c r="F32" s="5" t="n"/>
+      <c r="G32" s="5" t="n"/>
+      <c r="H32" s="5" t="n"/>
+      <c r="I32" s="5" t="n"/>
+      <c r="J32" s="5" t="n"/>
+      <c r="K32" s="12" t="n"/>
+      <c r="L32" s="5" t="n"/>
+      <c r="M32" s="5" t="n"/>
+      <c r="N32" s="5" t="n"/>
+      <c r="O32" s="5" t="n"/>
+      <c r="P32" s="5" t="n"/>
+      <c r="Q32" s="5" t="n"/>
+      <c r="R32" s="5" t="n"/>
+      <c r="S32" s="12" t="n"/>
+      <c r="T32" s="5" t="n"/>
+      <c r="U32" s="5" t="n"/>
+      <c r="V32" s="5" t="n"/>
+      <c r="W32" s="5" t="n"/>
+      <c r="X32" s="5" t="n"/>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="11" t="n"/>
+      <c r="B33" s="5" t="n"/>
+      <c r="C33" s="5" t="n"/>
+      <c r="D33" s="5" t="n"/>
+      <c r="E33" s="12" t="n"/>
+      <c r="F33" s="5" t="n"/>
+      <c r="G33" s="5" t="n"/>
+      <c r="H33" s="5" t="n"/>
+      <c r="I33" s="5" t="n"/>
+      <c r="J33" s="5" t="n"/>
+      <c r="K33" s="12" t="n"/>
+      <c r="L33" s="5" t="n"/>
+      <c r="M33" s="5" t="n"/>
+      <c r="N33" s="5" t="n"/>
+      <c r="O33" s="5" t="n"/>
+      <c r="P33" s="5" t="n"/>
+      <c r="Q33" s="5" t="n"/>
+      <c r="R33" s="5" t="n"/>
+      <c r="S33" s="12" t="n"/>
+      <c r="T33" s="5" t="n"/>
+      <c r="U33" s="5" t="n"/>
+      <c r="V33" s="5" t="n"/>
+      <c r="W33" s="5" t="n"/>
+      <c r="X33" s="5" t="n"/>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="11" t="n"/>
+      <c r="B34" s="5" t="n"/>
+      <c r="C34" s="5" t="n"/>
+      <c r="D34" s="5" t="n"/>
+      <c r="E34" s="12" t="n"/>
+      <c r="F34" s="5" t="n"/>
+      <c r="G34" s="5" t="n"/>
+      <c r="H34" s="5" t="n"/>
+      <c r="I34" s="5" t="n"/>
+      <c r="J34" s="5" t="n"/>
+      <c r="K34" s="12" t="n"/>
+      <c r="L34" s="5" t="n"/>
+      <c r="M34" s="5" t="n"/>
+      <c r="N34" s="5" t="n"/>
+      <c r="O34" s="5" t="n"/>
+      <c r="P34" s="5" t="n"/>
+      <c r="Q34" s="5" t="n"/>
+      <c r="R34" s="5" t="n"/>
+      <c r="S34" s="12" t="n"/>
+      <c r="T34" s="5" t="n"/>
+      <c r="U34" s="5" t="n"/>
+      <c r="V34" s="5" t="n"/>
+      <c r="W34" s="5" t="n"/>
+      <c r="X34" s="5" t="n"/>
+    </row>
+    <row r="35" ht="6" customHeight="1"/>
+    <row r="36" ht="34" customHeight="1">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  최초 신고 담당(119)</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n"/>
+      <c r="C36" s="5" t="n"/>
+      <c r="D36" s="5" t="n"/>
+      <c r="E36" s="5" t="n"/>
+      <c r="F36" s="5" t="n"/>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>정안전 (부재 시 이감독)</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="n"/>
+      <c r="I36" s="5" t="n"/>
+      <c r="J36" s="5" t="n"/>
+      <c r="K36" s="5" t="n"/>
+      <c r="L36" s="5" t="n"/>
+      <c r="M36" s="5" t="n"/>
+      <c r="N36" s="5" t="n"/>
+      <c r="O36" s="5" t="n"/>
+      <c r="P36" s="5" t="n"/>
+      <c r="Q36" s="5" t="n"/>
+      <c r="R36" s="5" t="n"/>
+      <c r="S36" s="5" t="n"/>
+      <c r="T36" s="5" t="n"/>
+      <c r="U36" s="5" t="n"/>
+      <c r="V36" s="5" t="n"/>
+      <c r="W36" s="5" t="n"/>
+      <c r="X36" s="5" t="n"/>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  현장 지휘</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n"/>
+      <c r="C37" s="5" t="n"/>
+      <c r="D37" s="5" t="n"/>
+      <c r="E37" s="5" t="n"/>
+      <c r="F37" s="5" t="n"/>
+      <c r="G37" s="6" t="inlineStr">
+        <is>
+          <t>김철수(현장대리인)</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="n"/>
+      <c r="I37" s="5" t="n"/>
+      <c r="J37" s="5" t="n"/>
+      <c r="K37" s="5" t="n"/>
+      <c r="L37" s="5" t="n"/>
+      <c r="M37" s="5" t="n"/>
+      <c r="N37" s="5" t="n"/>
+      <c r="O37" s="5" t="n"/>
+      <c r="P37" s="5" t="n"/>
+      <c r="Q37" s="5" t="n"/>
+      <c r="R37" s="5" t="n"/>
+      <c r="S37" s="5" t="n"/>
+      <c r="T37" s="5" t="n"/>
+      <c r="U37" s="5" t="n"/>
+      <c r="V37" s="5" t="n"/>
+      <c r="W37" s="5" t="n"/>
+      <c r="X37" s="5" t="n"/>
+    </row>
+    <row r="38" ht="24" customHeight="1">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  발주처·감리 연락</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n"/>
+      <c r="C38" s="5" t="n"/>
+      <c r="D38" s="5" t="n"/>
+      <c r="E38" s="5" t="n"/>
+      <c r="F38" s="5" t="n"/>
+      <c r="G38" s="6" t="inlineStr">
+        <is>
+          <t>오공무</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="n"/>
+      <c r="I38" s="5" t="n"/>
+      <c r="J38" s="5" t="n"/>
+      <c r="K38" s="5" t="n"/>
+      <c r="L38" s="5" t="n"/>
+      <c r="M38" s="5" t="n"/>
+      <c r="N38" s="5" t="n"/>
+      <c r="O38" s="5" t="n"/>
+      <c r="P38" s="5" t="n"/>
+      <c r="Q38" s="5" t="n"/>
+      <c r="R38" s="5" t="n"/>
+      <c r="S38" s="5" t="n"/>
+      <c r="T38" s="5" t="n"/>
+      <c r="U38" s="5" t="n"/>
+      <c r="V38" s="5" t="n"/>
+      <c r="W38" s="5" t="n"/>
+      <c r="X38" s="5" t="n"/>
+    </row>
+    <row r="39" ht="6" customHeight="1"/>
+    <row r="40" ht="10" customHeight="1"/>
+    <row r="41" ht="26" customHeight="1">
+      <c r="A41" s="13" t="n">
+        <v>46294</v>
+      </c>
+    </row>
+    <row r="42" ht="24" customHeight="1">
+      <c r="A42" s="14" t="inlineStr"/>
+      <c r="K42" s="15" t="inlineStr">
+        <is>
+          <t>현장대리인</t>
+        </is>
+      </c>
+      <c r="Q42" s="16" t="inlineStr">
+        <is>
+          <t>김철수</t>
+        </is>
+      </c>
+      <c r="U42" s="17" t="inlineStr">
+        <is>
+          <t>(서명 또는 인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="24" customHeight="1">
+      <c r="A43" s="14" t="inlineStr"/>
+      <c r="K43" s="15" t="inlineStr">
+        <is>
+          <t>안전관리자</t>
+        </is>
+      </c>
+      <c r="Q43" s="16" t="inlineStr">
+        <is>
+          <t>정안전</t>
+        </is>
+      </c>
+      <c r="U43" s="17" t="inlineStr">
+        <is>
+          <t>(서명 또는 인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="6" customHeight="1"/>
+    <row r="46" ht="19.5" customHeight="1">
+      <c r="A46" s="18" t="inlineStr">
+        <is>
+          <t>이 시트는 작성 예시입니다(가상의 현장 · 이름 · 금액). 실제로는 앞 시트에 적으세요.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="117">
+    <mergeCell ref="I14:L14"/>
+    <mergeCell ref="M18:S18"/>
+    <mergeCell ref="T15:X15"/>
+    <mergeCell ref="E28:J28"/>
+    <mergeCell ref="K34:R34"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="M17:S17"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="S28:X28"/>
+    <mergeCell ref="A43:J43"/>
+    <mergeCell ref="E30:J30"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A3:X3"/>
+    <mergeCell ref="M19:S19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="K29:R29"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="K31:R31"/>
+    <mergeCell ref="S29:X29"/>
+    <mergeCell ref="A38:F38"/>
+    <mergeCell ref="E32:J32"/>
+    <mergeCell ref="I16:L16"/>
+    <mergeCell ref="S31:X31"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="T22:X22"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="I18:L18"/>
+    <mergeCell ref="A24:X24"/>
+    <mergeCell ref="M13:S13"/>
+    <mergeCell ref="M21:S21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="U42:X42"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="G7:X7"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="G38:X38"/>
+    <mergeCell ref="T20:X20"/>
+    <mergeCell ref="T14:X14"/>
+    <mergeCell ref="K33:R33"/>
+    <mergeCell ref="I20:L20"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="E34:J34"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="E22:H22"/>
+    <mergeCell ref="I13:L13"/>
+    <mergeCell ref="S34:X34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="E21:H21"/>
+    <mergeCell ref="I15:L15"/>
+    <mergeCell ref="S30:X30"/>
+    <mergeCell ref="E14:H14"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="G9:X9"/>
+    <mergeCell ref="T17:X17"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="T19:X19"/>
+    <mergeCell ref="M15:S15"/>
+    <mergeCell ref="U43:X43"/>
+    <mergeCell ref="A42:J42"/>
+    <mergeCell ref="I17:L17"/>
+    <mergeCell ref="G37:X37"/>
+    <mergeCell ref="E16:H16"/>
+    <mergeCell ref="A41:X41"/>
+    <mergeCell ref="I19:L19"/>
+    <mergeCell ref="K43:P43"/>
+    <mergeCell ref="E18:H18"/>
+    <mergeCell ref="K26:R26"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="S33:X33"/>
+    <mergeCell ref="K42:P42"/>
+    <mergeCell ref="E27:J27"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="Q42:T42"/>
+    <mergeCell ref="T21:X21"/>
+    <mergeCell ref="E20:H20"/>
+    <mergeCell ref="K27:R27"/>
+    <mergeCell ref="M20:S20"/>
+    <mergeCell ref="E13:H13"/>
+    <mergeCell ref="T13:X13"/>
+    <mergeCell ref="T16:X16"/>
+    <mergeCell ref="A36:F36"/>
+    <mergeCell ref="I21:L21"/>
+    <mergeCell ref="M22:S22"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="G36:X36"/>
+    <mergeCell ref="A11:X11"/>
+    <mergeCell ref="E15:H15"/>
+    <mergeCell ref="K28:R28"/>
+    <mergeCell ref="T18:X18"/>
+    <mergeCell ref="A32:D32"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="E29:J29"/>
+    <mergeCell ref="K30:R30"/>
+    <mergeCell ref="A37:F37"/>
+    <mergeCell ref="E31:J31"/>
+    <mergeCell ref="G6:X6"/>
+    <mergeCell ref="A46:X46"/>
+    <mergeCell ref="M14:S14"/>
+    <mergeCell ref="G5:X5"/>
+    <mergeCell ref="Q43:T43"/>
+    <mergeCell ref="K32:R32"/>
+    <mergeCell ref="E26:J26"/>
+    <mergeCell ref="E17:H17"/>
+    <mergeCell ref="S32:X32"/>
+    <mergeCell ref="S26:X26"/>
+    <mergeCell ref="E19:H19"/>
+    <mergeCell ref="I22:L22"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="E33:J33"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="S27:X27"/>
+    <mergeCell ref="M16:S16"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="M1:X1"/>
+    <mergeCell ref="G8:X8"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/web/public/forms/hyeonjang-jojikdo.xlsx
+++ b/web/public/forms/hyeonjang-jojikdo.xlsx
@@ -581,7 +581,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="M1" s="2" t="inlineStr">
@@ -1606,7 +1606,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="M1" s="19" t="inlineStr">

--- a/web/public/forms/hyeonjang-jojikdo.xlsx
+++ b/web/public/forms/hyeonjang-jojikdo.xlsx
@@ -8,11 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="현장 조직도 · 비상 조직도" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="작성 예시" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'현장 조직도 · 비상 조직도'!$A$1:$X$44</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'작성 예시'!$A$1:$X$44</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -127,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -180,9 +178,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1426,6 +1421,7 @@
       </c>
     </row>
     <row r="44" ht="6" customHeight="1"/>
+    <row r="45"/>
     <row r="46" ht="34" customHeight="1">
       <c r="A46" s="18" t="inlineStr">
         <is>
@@ -1565,1219 +1561,4 @@
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00F59E0B"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:X46"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="3.6" customWidth="1" min="1" max="1"/>
-    <col width="3.6" customWidth="1" min="2" max="2"/>
-    <col width="3.6" customWidth="1" min="3" max="3"/>
-    <col width="3.6" customWidth="1" min="4" max="4"/>
-    <col width="3.6" customWidth="1" min="5" max="5"/>
-    <col width="3.6" customWidth="1" min="6" max="6"/>
-    <col width="3.6" customWidth="1" min="7" max="7"/>
-    <col width="3.6" customWidth="1" min="8" max="8"/>
-    <col width="3.6" customWidth="1" min="9" max="9"/>
-    <col width="3.6" customWidth="1" min="10" max="10"/>
-    <col width="3.6" customWidth="1" min="11" max="11"/>
-    <col width="3.6" customWidth="1" min="12" max="12"/>
-    <col width="3.6" customWidth="1" min="13" max="13"/>
-    <col width="3.6" customWidth="1" min="14" max="14"/>
-    <col width="3.6" customWidth="1" min="15" max="15"/>
-    <col width="3.6" customWidth="1" min="16" max="16"/>
-    <col width="3.6" customWidth="1" min="17" max="17"/>
-    <col width="3.6" customWidth="1" min="18" max="18"/>
-    <col width="3.6" customWidth="1" min="19" max="19"/>
-    <col width="3.6" customWidth="1" min="20" max="20"/>
-    <col width="3.6" customWidth="1" min="21" max="21"/>
-    <col width="3.6" customWidth="1" min="22" max="22"/>
-    <col width="3.6" customWidth="1" min="23" max="23"/>
-    <col width="3.6" customWidth="1" min="24" max="24"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
-        </is>
-      </c>
-      <c r="M1" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">작성 예시 (가상의 현장)  </t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="6" customHeight="1"/>
-    <row r="3" ht="38" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>현 장  조 직 도  ·  비 상  조 직 도</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="10" customHeight="1"/>
-    <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  공 사 명</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n"/>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>가나지구 배수로 정비공사</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="n"/>
-      <c r="I5" s="5" t="n"/>
-      <c r="J5" s="5" t="n"/>
-      <c r="K5" s="5" t="n"/>
-      <c r="L5" s="5" t="n"/>
-      <c r="M5" s="5" t="n"/>
-      <c r="N5" s="5" t="n"/>
-      <c r="O5" s="5" t="n"/>
-      <c r="P5" s="5" t="n"/>
-      <c r="Q5" s="5" t="n"/>
-      <c r="R5" s="5" t="n"/>
-      <c r="S5" s="5" t="n"/>
-      <c r="T5" s="5" t="n"/>
-      <c r="U5" s="5" t="n"/>
-      <c r="V5" s="5" t="n"/>
-      <c r="W5" s="5" t="n"/>
-      <c r="X5" s="5" t="n"/>
-    </row>
-    <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  발 주 기 관</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>가나시 건설과</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="n"/>
-      <c r="I6" s="5" t="n"/>
-      <c r="J6" s="5" t="n"/>
-      <c r="K6" s="5" t="n"/>
-      <c r="L6" s="5" t="n"/>
-      <c r="M6" s="5" t="n"/>
-      <c r="N6" s="5" t="n"/>
-      <c r="O6" s="5" t="n"/>
-      <c r="P6" s="5" t="n"/>
-      <c r="Q6" s="5" t="n"/>
-      <c r="R6" s="5" t="n"/>
-      <c r="S6" s="5" t="n"/>
-      <c r="T6" s="5" t="n"/>
-      <c r="U6" s="5" t="n"/>
-      <c r="V6" s="5" t="n"/>
-      <c r="W6" s="5" t="n"/>
-      <c r="X6" s="5" t="n"/>
-    </row>
-    <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  계 약 금 액</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
-      <c r="G7" s="7" t="n">
-        <v>963241000</v>
-      </c>
-      <c r="H7" s="5" t="n"/>
-      <c r="I7" s="5" t="n"/>
-      <c r="J7" s="5" t="n"/>
-      <c r="K7" s="5" t="n"/>
-      <c r="L7" s="5" t="n"/>
-      <c r="M7" s="5" t="n"/>
-      <c r="N7" s="5" t="n"/>
-      <c r="O7" s="5" t="n"/>
-      <c r="P7" s="5" t="n"/>
-      <c r="Q7" s="5" t="n"/>
-      <c r="R7" s="5" t="n"/>
-      <c r="S7" s="5" t="n"/>
-      <c r="T7" s="5" t="n"/>
-      <c r="U7" s="5" t="n"/>
-      <c r="V7" s="5" t="n"/>
-      <c r="W7" s="5" t="n"/>
-      <c r="X7" s="5" t="n"/>
-    </row>
-    <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  공        기</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>2026. 3. 9. ~ 2026. 12. 31. (298일)</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="n"/>
-      <c r="I8" s="5" t="n"/>
-      <c r="J8" s="5" t="n"/>
-      <c r="K8" s="5" t="n"/>
-      <c r="L8" s="5" t="n"/>
-      <c r="M8" s="5" t="n"/>
-      <c r="N8" s="5" t="n"/>
-      <c r="O8" s="5" t="n"/>
-      <c r="P8" s="5" t="n"/>
-      <c r="Q8" s="5" t="n"/>
-      <c r="R8" s="5" t="n"/>
-      <c r="S8" s="5" t="n"/>
-      <c r="T8" s="5" t="n"/>
-      <c r="U8" s="5" t="n"/>
-      <c r="V8" s="5" t="n"/>
-      <c r="W8" s="5" t="n"/>
-      <c r="X8" s="5" t="n"/>
-    </row>
-    <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  작 성 일 자</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="8" t="n">
-        <v>46294</v>
-      </c>
-      <c r="H9" s="5" t="n"/>
-      <c r="I9" s="5" t="n"/>
-      <c r="J9" s="5" t="n"/>
-      <c r="K9" s="5" t="n"/>
-      <c r="L9" s="5" t="n"/>
-      <c r="M9" s="5" t="n"/>
-      <c r="N9" s="5" t="n"/>
-      <c r="O9" s="5" t="n"/>
-      <c r="P9" s="5" t="n"/>
-      <c r="Q9" s="5" t="n"/>
-      <c r="R9" s="5" t="n"/>
-      <c r="S9" s="5" t="n"/>
-      <c r="T9" s="5" t="n"/>
-      <c r="U9" s="5" t="n"/>
-      <c r="V9" s="5" t="n"/>
-      <c r="W9" s="5" t="n"/>
-      <c r="X9" s="5" t="n"/>
-    </row>
-    <row r="10" ht="6" customHeight="1"/>
-    <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>■ 평상시 조직</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="6" customHeight="1"/>
-    <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>구분</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="10" t="inlineStr">
-        <is>
-          <t>직책</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="5" t="n"/>
-      <c r="H13" s="5" t="n"/>
-      <c r="I13" s="10" t="inlineStr">
-        <is>
-          <t>성명</t>
-        </is>
-      </c>
-      <c r="J13" s="5" t="n"/>
-      <c r="K13" s="5" t="n"/>
-      <c r="L13" s="5" t="n"/>
-      <c r="M13" s="10" t="inlineStr">
-        <is>
-          <t>담당 업무</t>
-        </is>
-      </c>
-      <c r="N13" s="5" t="n"/>
-      <c r="O13" s="5" t="n"/>
-      <c r="P13" s="5" t="n"/>
-      <c r="Q13" s="5" t="n"/>
-      <c r="R13" s="5" t="n"/>
-      <c r="S13" s="5" t="n"/>
-      <c r="T13" s="10" t="inlineStr">
-        <is>
-          <t>연락처</t>
-        </is>
-      </c>
-      <c r="U13" s="5" t="n"/>
-      <c r="V13" s="5" t="n"/>
-      <c r="W13" s="5" t="n"/>
-      <c r="X13" s="5" t="n"/>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="11" t="inlineStr">
-        <is>
-          <t>총괄</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="n"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="11" t="inlineStr">
-        <is>
-          <t>현장대리인</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="5" t="n"/>
-      <c r="H14" s="5" t="n"/>
-      <c r="I14" s="11" t="inlineStr">
-        <is>
-          <t>김철수</t>
-        </is>
-      </c>
-      <c r="J14" s="5" t="n"/>
-      <c r="K14" s="5" t="n"/>
-      <c r="L14" s="5" t="n"/>
-      <c r="M14" s="12" t="inlineStr">
-        <is>
-          <t>현장 총괄</t>
-        </is>
-      </c>
-      <c r="N14" s="5" t="n"/>
-      <c r="O14" s="5" t="n"/>
-      <c r="P14" s="5" t="n"/>
-      <c r="Q14" s="5" t="n"/>
-      <c r="R14" s="5" t="n"/>
-      <c r="S14" s="5" t="n"/>
-      <c r="T14" s="11" t="inlineStr">
-        <is>
-          <t>000-0000-0000</t>
-        </is>
-      </c>
-      <c r="U14" s="5" t="n"/>
-      <c r="V14" s="5" t="n"/>
-      <c r="W14" s="5" t="n"/>
-      <c r="X14" s="5" t="n"/>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t>공사</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="11" t="inlineStr">
-        <is>
-          <t>공사과장</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="5" t="n"/>
-      <c r="H15" s="5" t="n"/>
-      <c r="I15" s="11" t="inlineStr">
-        <is>
-          <t>이감독</t>
-        </is>
-      </c>
-      <c r="J15" s="5" t="n"/>
-      <c r="K15" s="5" t="n"/>
-      <c r="L15" s="5" t="n"/>
-      <c r="M15" s="12" t="inlineStr">
-        <is>
-          <t>작업 지휘</t>
-        </is>
-      </c>
-      <c r="N15" s="5" t="n"/>
-      <c r="O15" s="5" t="n"/>
-      <c r="P15" s="5" t="n"/>
-      <c r="Q15" s="5" t="n"/>
-      <c r="R15" s="5" t="n"/>
-      <c r="S15" s="5" t="n"/>
-      <c r="T15" s="11" t="inlineStr">
-        <is>
-          <t>000-0000-0000</t>
-        </is>
-      </c>
-      <c r="U15" s="5" t="n"/>
-      <c r="V15" s="5" t="n"/>
-      <c r="W15" s="5" t="n"/>
-      <c r="X15" s="5" t="n"/>
-    </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="11" t="inlineStr">
-        <is>
-          <t>안전</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="n"/>
-      <c r="C16" s="5" t="n"/>
-      <c r="D16" s="5" t="n"/>
-      <c r="E16" s="11" t="inlineStr">
-        <is>
-          <t>안전관리자</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="n"/>
-      <c r="G16" s="5" t="n"/>
-      <c r="H16" s="5" t="n"/>
-      <c r="I16" s="11" t="inlineStr">
-        <is>
-          <t>정안전</t>
-        </is>
-      </c>
-      <c r="J16" s="5" t="n"/>
-      <c r="K16" s="5" t="n"/>
-      <c r="L16" s="5" t="n"/>
-      <c r="M16" s="12" t="inlineStr">
-        <is>
-          <t>안전 점검·교육</t>
-        </is>
-      </c>
-      <c r="N16" s="5" t="n"/>
-      <c r="O16" s="5" t="n"/>
-      <c r="P16" s="5" t="n"/>
-      <c r="Q16" s="5" t="n"/>
-      <c r="R16" s="5" t="n"/>
-      <c r="S16" s="5" t="n"/>
-      <c r="T16" s="11" t="inlineStr">
-        <is>
-          <t>000-0000-0000</t>
-        </is>
-      </c>
-      <c r="U16" s="5" t="n"/>
-      <c r="V16" s="5" t="n"/>
-      <c r="W16" s="5" t="n"/>
-      <c r="X16" s="5" t="n"/>
-    </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t>품질</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="n"/>
-      <c r="C17" s="5" t="n"/>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="11" t="inlineStr">
-        <is>
-          <t>품질관리자</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="n"/>
-      <c r="G17" s="5" t="n"/>
-      <c r="H17" s="5" t="n"/>
-      <c r="I17" s="11" t="inlineStr">
-        <is>
-          <t>한품질</t>
-        </is>
-      </c>
-      <c r="J17" s="5" t="n"/>
-      <c r="K17" s="5" t="n"/>
-      <c r="L17" s="5" t="n"/>
-      <c r="M17" s="12" t="inlineStr">
-        <is>
-          <t>시험·검사</t>
-        </is>
-      </c>
-      <c r="N17" s="5" t="n"/>
-      <c r="O17" s="5" t="n"/>
-      <c r="P17" s="5" t="n"/>
-      <c r="Q17" s="5" t="n"/>
-      <c r="R17" s="5" t="n"/>
-      <c r="S17" s="5" t="n"/>
-      <c r="T17" s="11" t="inlineStr">
-        <is>
-          <t>000-0000-0000</t>
-        </is>
-      </c>
-      <c r="U17" s="5" t="n"/>
-      <c r="V17" s="5" t="n"/>
-      <c r="W17" s="5" t="n"/>
-      <c r="X17" s="5" t="n"/>
-    </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="11" t="inlineStr">
-        <is>
-          <t>공무</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="n"/>
-      <c r="C18" s="5" t="n"/>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="11" t="inlineStr">
-        <is>
-          <t>공무</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="n"/>
-      <c r="G18" s="5" t="n"/>
-      <c r="H18" s="5" t="n"/>
-      <c r="I18" s="11" t="inlineStr">
-        <is>
-          <t>오공무</t>
-        </is>
-      </c>
-      <c r="J18" s="5" t="n"/>
-      <c r="K18" s="5" t="n"/>
-      <c r="L18" s="5" t="n"/>
-      <c r="M18" s="12" t="inlineStr">
-        <is>
-          <t>서류·기성</t>
-        </is>
-      </c>
-      <c r="N18" s="5" t="n"/>
-      <c r="O18" s="5" t="n"/>
-      <c r="P18" s="5" t="n"/>
-      <c r="Q18" s="5" t="n"/>
-      <c r="R18" s="5" t="n"/>
-      <c r="S18" s="5" t="n"/>
-      <c r="T18" s="11" t="inlineStr">
-        <is>
-          <t>000-0000-0000</t>
-        </is>
-      </c>
-      <c r="U18" s="5" t="n"/>
-      <c r="V18" s="5" t="n"/>
-      <c r="W18" s="5" t="n"/>
-      <c r="X18" s="5" t="n"/>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="11" t="n"/>
-      <c r="B19" s="5" t="n"/>
-      <c r="C19" s="5" t="n"/>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="11" t="n"/>
-      <c r="F19" s="5" t="n"/>
-      <c r="G19" s="5" t="n"/>
-      <c r="H19" s="5" t="n"/>
-      <c r="I19" s="11" t="n"/>
-      <c r="J19" s="5" t="n"/>
-      <c r="K19" s="5" t="n"/>
-      <c r="L19" s="5" t="n"/>
-      <c r="M19" s="12" t="n"/>
-      <c r="N19" s="5" t="n"/>
-      <c r="O19" s="5" t="n"/>
-      <c r="P19" s="5" t="n"/>
-      <c r="Q19" s="5" t="n"/>
-      <c r="R19" s="5" t="n"/>
-      <c r="S19" s="5" t="n"/>
-      <c r="T19" s="11" t="n"/>
-      <c r="U19" s="5" t="n"/>
-      <c r="V19" s="5" t="n"/>
-      <c r="W19" s="5" t="n"/>
-      <c r="X19" s="5" t="n"/>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="11" t="n"/>
-      <c r="B20" s="5" t="n"/>
-      <c r="C20" s="5" t="n"/>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="11" t="n"/>
-      <c r="F20" s="5" t="n"/>
-      <c r="G20" s="5" t="n"/>
-      <c r="H20" s="5" t="n"/>
-      <c r="I20" s="11" t="n"/>
-      <c r="J20" s="5" t="n"/>
-      <c r="K20" s="5" t="n"/>
-      <c r="L20" s="5" t="n"/>
-      <c r="M20" s="12" t="n"/>
-      <c r="N20" s="5" t="n"/>
-      <c r="O20" s="5" t="n"/>
-      <c r="P20" s="5" t="n"/>
-      <c r="Q20" s="5" t="n"/>
-      <c r="R20" s="5" t="n"/>
-      <c r="S20" s="5" t="n"/>
-      <c r="T20" s="11" t="n"/>
-      <c r="U20" s="5" t="n"/>
-      <c r="V20" s="5" t="n"/>
-      <c r="W20" s="5" t="n"/>
-      <c r="X20" s="5" t="n"/>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="11" t="n"/>
-      <c r="B21" s="5" t="n"/>
-      <c r="C21" s="5" t="n"/>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="11" t="n"/>
-      <c r="F21" s="5" t="n"/>
-      <c r="G21" s="5" t="n"/>
-      <c r="H21" s="5" t="n"/>
-      <c r="I21" s="11" t="n"/>
-      <c r="J21" s="5" t="n"/>
-      <c r="K21" s="5" t="n"/>
-      <c r="L21" s="5" t="n"/>
-      <c r="M21" s="12" t="n"/>
-      <c r="N21" s="5" t="n"/>
-      <c r="O21" s="5" t="n"/>
-      <c r="P21" s="5" t="n"/>
-      <c r="Q21" s="5" t="n"/>
-      <c r="R21" s="5" t="n"/>
-      <c r="S21" s="5" t="n"/>
-      <c r="T21" s="11" t="n"/>
-      <c r="U21" s="5" t="n"/>
-      <c r="V21" s="5" t="n"/>
-      <c r="W21" s="5" t="n"/>
-      <c r="X21" s="5" t="n"/>
-    </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="11" t="n"/>
-      <c r="B22" s="5" t="n"/>
-      <c r="C22" s="5" t="n"/>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="11" t="n"/>
-      <c r="F22" s="5" t="n"/>
-      <c r="G22" s="5" t="n"/>
-      <c r="H22" s="5" t="n"/>
-      <c r="I22" s="11" t="n"/>
-      <c r="J22" s="5" t="n"/>
-      <c r="K22" s="5" t="n"/>
-      <c r="L22" s="5" t="n"/>
-      <c r="M22" s="12" t="n"/>
-      <c r="N22" s="5" t="n"/>
-      <c r="O22" s="5" t="n"/>
-      <c r="P22" s="5" t="n"/>
-      <c r="Q22" s="5" t="n"/>
-      <c r="R22" s="5" t="n"/>
-      <c r="S22" s="5" t="n"/>
-      <c r="T22" s="11" t="n"/>
-      <c r="U22" s="5" t="n"/>
-      <c r="V22" s="5" t="n"/>
-      <c r="W22" s="5" t="n"/>
-      <c r="X22" s="5" t="n"/>
-    </row>
-    <row r="23" ht="6" customHeight="1"/>
-    <row r="24" ht="26" customHeight="1">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>■ 비상시 조직 (사고·재해 발생 시)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="6" customHeight="1"/>
-    <row r="26" ht="24" customHeight="1">
-      <c r="A26" s="10" t="inlineStr">
-        <is>
-          <t>구분</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="n"/>
-      <c r="C26" s="5" t="n"/>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="10" t="inlineStr">
-        <is>
-          <t>직책·성명</t>
-        </is>
-      </c>
-      <c r="F26" s="5" t="n"/>
-      <c r="G26" s="5" t="n"/>
-      <c r="H26" s="5" t="n"/>
-      <c r="I26" s="5" t="n"/>
-      <c r="J26" s="5" t="n"/>
-      <c r="K26" s="10" t="inlineStr">
-        <is>
-          <t>비상시 임무</t>
-        </is>
-      </c>
-      <c r="L26" s="5" t="n"/>
-      <c r="M26" s="5" t="n"/>
-      <c r="N26" s="5" t="n"/>
-      <c r="O26" s="5" t="n"/>
-      <c r="P26" s="5" t="n"/>
-      <c r="Q26" s="5" t="n"/>
-      <c r="R26" s="5" t="n"/>
-      <c r="S26" s="10" t="inlineStr">
-        <is>
-          <t>연락처</t>
-        </is>
-      </c>
-      <c r="T26" s="5" t="n"/>
-      <c r="U26" s="5" t="n"/>
-      <c r="V26" s="5" t="n"/>
-      <c r="W26" s="5" t="n"/>
-      <c r="X26" s="5" t="n"/>
-    </row>
-    <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="11" t="inlineStr">
-        <is>
-          <t>지휘</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="n"/>
-      <c r="C27" s="5" t="n"/>
-      <c r="D27" s="5" t="n"/>
-      <c r="E27" s="12" t="inlineStr">
-        <is>
-          <t>현장대리인 김철수</t>
-        </is>
-      </c>
-      <c r="F27" s="5" t="n"/>
-      <c r="G27" s="5" t="n"/>
-      <c r="H27" s="5" t="n"/>
-      <c r="I27" s="5" t="n"/>
-      <c r="J27" s="5" t="n"/>
-      <c r="K27" s="12" t="inlineStr">
-        <is>
-          <t>상황 지휘 · 작업 중지</t>
-        </is>
-      </c>
-      <c r="L27" s="5" t="n"/>
-      <c r="M27" s="5" t="n"/>
-      <c r="N27" s="5" t="n"/>
-      <c r="O27" s="5" t="n"/>
-      <c r="P27" s="5" t="n"/>
-      <c r="Q27" s="5" t="n"/>
-      <c r="R27" s="5" t="n"/>
-      <c r="S27" s="12" t="inlineStr">
-        <is>
-          <t>000-0000-0000</t>
-        </is>
-      </c>
-      <c r="T27" s="5" t="n"/>
-      <c r="U27" s="5" t="n"/>
-      <c r="V27" s="5" t="n"/>
-      <c r="W27" s="5" t="n"/>
-      <c r="X27" s="5" t="n"/>
-    </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="11" t="inlineStr">
-        <is>
-          <t>신고</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="n"/>
-      <c r="C28" s="5" t="n"/>
-      <c r="D28" s="5" t="n"/>
-      <c r="E28" s="12" t="inlineStr">
-        <is>
-          <t>안전관리자 정안전</t>
-        </is>
-      </c>
-      <c r="F28" s="5" t="n"/>
-      <c r="G28" s="5" t="n"/>
-      <c r="H28" s="5" t="n"/>
-      <c r="I28" s="5" t="n"/>
-      <c r="J28" s="5" t="n"/>
-      <c r="K28" s="12" t="inlineStr">
-        <is>
-          <t>119 신고 · 응급조치</t>
-        </is>
-      </c>
-      <c r="L28" s="5" t="n"/>
-      <c r="M28" s="5" t="n"/>
-      <c r="N28" s="5" t="n"/>
-      <c r="O28" s="5" t="n"/>
-      <c r="P28" s="5" t="n"/>
-      <c r="Q28" s="5" t="n"/>
-      <c r="R28" s="5" t="n"/>
-      <c r="S28" s="12" t="inlineStr">
-        <is>
-          <t>000-0000-0000</t>
-        </is>
-      </c>
-      <c r="T28" s="5" t="n"/>
-      <c r="U28" s="5" t="n"/>
-      <c r="V28" s="5" t="n"/>
-      <c r="W28" s="5" t="n"/>
-      <c r="X28" s="5" t="n"/>
-    </row>
-    <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="11" t="inlineStr">
-        <is>
-          <t>구조</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="n"/>
-      <c r="C29" s="5" t="n"/>
-      <c r="D29" s="5" t="n"/>
-      <c r="E29" s="12" t="inlineStr">
-        <is>
-          <t>공사과장 이감독</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="n"/>
-      <c r="G29" s="5" t="n"/>
-      <c r="H29" s="5" t="n"/>
-      <c r="I29" s="5" t="n"/>
-      <c r="J29" s="5" t="n"/>
-      <c r="K29" s="12" t="inlineStr">
-        <is>
-          <t>구조 · 현장 통제</t>
-        </is>
-      </c>
-      <c r="L29" s="5" t="n"/>
-      <c r="M29" s="5" t="n"/>
-      <c r="N29" s="5" t="n"/>
-      <c r="O29" s="5" t="n"/>
-      <c r="P29" s="5" t="n"/>
-      <c r="Q29" s="5" t="n"/>
-      <c r="R29" s="5" t="n"/>
-      <c r="S29" s="12" t="inlineStr">
-        <is>
-          <t>000-0000-0000</t>
-        </is>
-      </c>
-      <c r="T29" s="5" t="n"/>
-      <c r="U29" s="5" t="n"/>
-      <c r="V29" s="5" t="n"/>
-      <c r="W29" s="5" t="n"/>
-      <c r="X29" s="5" t="n"/>
-    </row>
-    <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="11" t="inlineStr">
-        <is>
-          <t>연락</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="n"/>
-      <c r="C30" s="5" t="n"/>
-      <c r="D30" s="5" t="n"/>
-      <c r="E30" s="12" t="inlineStr">
-        <is>
-          <t>공무 오공무</t>
-        </is>
-      </c>
-      <c r="F30" s="5" t="n"/>
-      <c r="G30" s="5" t="n"/>
-      <c r="H30" s="5" t="n"/>
-      <c r="I30" s="5" t="n"/>
-      <c r="J30" s="5" t="n"/>
-      <c r="K30" s="12" t="inlineStr">
-        <is>
-          <t>발주처·감리·본사 보고</t>
-        </is>
-      </c>
-      <c r="L30" s="5" t="n"/>
-      <c r="M30" s="5" t="n"/>
-      <c r="N30" s="5" t="n"/>
-      <c r="O30" s="5" t="n"/>
-      <c r="P30" s="5" t="n"/>
-      <c r="Q30" s="5" t="n"/>
-      <c r="R30" s="5" t="n"/>
-      <c r="S30" s="12" t="inlineStr">
-        <is>
-          <t>000-0000-0000</t>
-        </is>
-      </c>
-      <c r="T30" s="5" t="n"/>
-      <c r="U30" s="5" t="n"/>
-      <c r="V30" s="5" t="n"/>
-      <c r="W30" s="5" t="n"/>
-      <c r="X30" s="5" t="n"/>
-    </row>
-    <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="11" t="n"/>
-      <c r="B31" s="5" t="n"/>
-      <c r="C31" s="5" t="n"/>
-      <c r="D31" s="5" t="n"/>
-      <c r="E31" s="12" t="n"/>
-      <c r="F31" s="5" t="n"/>
-      <c r="G31" s="5" t="n"/>
-      <c r="H31" s="5" t="n"/>
-      <c r="I31" s="5" t="n"/>
-      <c r="J31" s="5" t="n"/>
-      <c r="K31" s="12" t="n"/>
-      <c r="L31" s="5" t="n"/>
-      <c r="M31" s="5" t="n"/>
-      <c r="N31" s="5" t="n"/>
-      <c r="O31" s="5" t="n"/>
-      <c r="P31" s="5" t="n"/>
-      <c r="Q31" s="5" t="n"/>
-      <c r="R31" s="5" t="n"/>
-      <c r="S31" s="12" t="n"/>
-      <c r="T31" s="5" t="n"/>
-      <c r="U31" s="5" t="n"/>
-      <c r="V31" s="5" t="n"/>
-      <c r="W31" s="5" t="n"/>
-      <c r="X31" s="5" t="n"/>
-    </row>
-    <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="11" t="n"/>
-      <c r="B32" s="5" t="n"/>
-      <c r="C32" s="5" t="n"/>
-      <c r="D32" s="5" t="n"/>
-      <c r="E32" s="12" t="n"/>
-      <c r="F32" s="5" t="n"/>
-      <c r="G32" s="5" t="n"/>
-      <c r="H32" s="5" t="n"/>
-      <c r="I32" s="5" t="n"/>
-      <c r="J32" s="5" t="n"/>
-      <c r="K32" s="12" t="n"/>
-      <c r="L32" s="5" t="n"/>
-      <c r="M32" s="5" t="n"/>
-      <c r="N32" s="5" t="n"/>
-      <c r="O32" s="5" t="n"/>
-      <c r="P32" s="5" t="n"/>
-      <c r="Q32" s="5" t="n"/>
-      <c r="R32" s="5" t="n"/>
-      <c r="S32" s="12" t="n"/>
-      <c r="T32" s="5" t="n"/>
-      <c r="U32" s="5" t="n"/>
-      <c r="V32" s="5" t="n"/>
-      <c r="W32" s="5" t="n"/>
-      <c r="X32" s="5" t="n"/>
-    </row>
-    <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="11" t="n"/>
-      <c r="B33" s="5" t="n"/>
-      <c r="C33" s="5" t="n"/>
-      <c r="D33" s="5" t="n"/>
-      <c r="E33" s="12" t="n"/>
-      <c r="F33" s="5" t="n"/>
-      <c r="G33" s="5" t="n"/>
-      <c r="H33" s="5" t="n"/>
-      <c r="I33" s="5" t="n"/>
-      <c r="J33" s="5" t="n"/>
-      <c r="K33" s="12" t="n"/>
-      <c r="L33" s="5" t="n"/>
-      <c r="M33" s="5" t="n"/>
-      <c r="N33" s="5" t="n"/>
-      <c r="O33" s="5" t="n"/>
-      <c r="P33" s="5" t="n"/>
-      <c r="Q33" s="5" t="n"/>
-      <c r="R33" s="5" t="n"/>
-      <c r="S33" s="12" t="n"/>
-      <c r="T33" s="5" t="n"/>
-      <c r="U33" s="5" t="n"/>
-      <c r="V33" s="5" t="n"/>
-      <c r="W33" s="5" t="n"/>
-      <c r="X33" s="5" t="n"/>
-    </row>
-    <row r="34" ht="22" customHeight="1">
-      <c r="A34" s="11" t="n"/>
-      <c r="B34" s="5" t="n"/>
-      <c r="C34" s="5" t="n"/>
-      <c r="D34" s="5" t="n"/>
-      <c r="E34" s="12" t="n"/>
-      <c r="F34" s="5" t="n"/>
-      <c r="G34" s="5" t="n"/>
-      <c r="H34" s="5" t="n"/>
-      <c r="I34" s="5" t="n"/>
-      <c r="J34" s="5" t="n"/>
-      <c r="K34" s="12" t="n"/>
-      <c r="L34" s="5" t="n"/>
-      <c r="M34" s="5" t="n"/>
-      <c r="N34" s="5" t="n"/>
-      <c r="O34" s="5" t="n"/>
-      <c r="P34" s="5" t="n"/>
-      <c r="Q34" s="5" t="n"/>
-      <c r="R34" s="5" t="n"/>
-      <c r="S34" s="12" t="n"/>
-      <c r="T34" s="5" t="n"/>
-      <c r="U34" s="5" t="n"/>
-      <c r="V34" s="5" t="n"/>
-      <c r="W34" s="5" t="n"/>
-      <c r="X34" s="5" t="n"/>
-    </row>
-    <row r="35" ht="6" customHeight="1"/>
-    <row r="36" ht="34" customHeight="1">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  최초 신고 담당(119)</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="n"/>
-      <c r="C36" s="5" t="n"/>
-      <c r="D36" s="5" t="n"/>
-      <c r="E36" s="5" t="n"/>
-      <c r="F36" s="5" t="n"/>
-      <c r="G36" s="6" t="inlineStr">
-        <is>
-          <t>정안전 (부재 시 이감독)</t>
-        </is>
-      </c>
-      <c r="H36" s="5" t="n"/>
-      <c r="I36" s="5" t="n"/>
-      <c r="J36" s="5" t="n"/>
-      <c r="K36" s="5" t="n"/>
-      <c r="L36" s="5" t="n"/>
-      <c r="M36" s="5" t="n"/>
-      <c r="N36" s="5" t="n"/>
-      <c r="O36" s="5" t="n"/>
-      <c r="P36" s="5" t="n"/>
-      <c r="Q36" s="5" t="n"/>
-      <c r="R36" s="5" t="n"/>
-      <c r="S36" s="5" t="n"/>
-      <c r="T36" s="5" t="n"/>
-      <c r="U36" s="5" t="n"/>
-      <c r="V36" s="5" t="n"/>
-      <c r="W36" s="5" t="n"/>
-      <c r="X36" s="5" t="n"/>
-    </row>
-    <row r="37" ht="24" customHeight="1">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  현장 지휘</t>
-        </is>
-      </c>
-      <c r="B37" s="5" t="n"/>
-      <c r="C37" s="5" t="n"/>
-      <c r="D37" s="5" t="n"/>
-      <c r="E37" s="5" t="n"/>
-      <c r="F37" s="5" t="n"/>
-      <c r="G37" s="6" t="inlineStr">
-        <is>
-          <t>김철수(현장대리인)</t>
-        </is>
-      </c>
-      <c r="H37" s="5" t="n"/>
-      <c r="I37" s="5" t="n"/>
-      <c r="J37" s="5" t="n"/>
-      <c r="K37" s="5" t="n"/>
-      <c r="L37" s="5" t="n"/>
-      <c r="M37" s="5" t="n"/>
-      <c r="N37" s="5" t="n"/>
-      <c r="O37" s="5" t="n"/>
-      <c r="P37" s="5" t="n"/>
-      <c r="Q37" s="5" t="n"/>
-      <c r="R37" s="5" t="n"/>
-      <c r="S37" s="5" t="n"/>
-      <c r="T37" s="5" t="n"/>
-      <c r="U37" s="5" t="n"/>
-      <c r="V37" s="5" t="n"/>
-      <c r="W37" s="5" t="n"/>
-      <c r="X37" s="5" t="n"/>
-    </row>
-    <row r="38" ht="24" customHeight="1">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  발주처·감리 연락</t>
-        </is>
-      </c>
-      <c r="B38" s="5" t="n"/>
-      <c r="C38" s="5" t="n"/>
-      <c r="D38" s="5" t="n"/>
-      <c r="E38" s="5" t="n"/>
-      <c r="F38" s="5" t="n"/>
-      <c r="G38" s="6" t="inlineStr">
-        <is>
-          <t>오공무</t>
-        </is>
-      </c>
-      <c r="H38" s="5" t="n"/>
-      <c r="I38" s="5" t="n"/>
-      <c r="J38" s="5" t="n"/>
-      <c r="K38" s="5" t="n"/>
-      <c r="L38" s="5" t="n"/>
-      <c r="M38" s="5" t="n"/>
-      <c r="N38" s="5" t="n"/>
-      <c r="O38" s="5" t="n"/>
-      <c r="P38" s="5" t="n"/>
-      <c r="Q38" s="5" t="n"/>
-      <c r="R38" s="5" t="n"/>
-      <c r="S38" s="5" t="n"/>
-      <c r="T38" s="5" t="n"/>
-      <c r="U38" s="5" t="n"/>
-      <c r="V38" s="5" t="n"/>
-      <c r="W38" s="5" t="n"/>
-      <c r="X38" s="5" t="n"/>
-    </row>
-    <row r="39" ht="6" customHeight="1"/>
-    <row r="40" ht="10" customHeight="1"/>
-    <row r="41" ht="26" customHeight="1">
-      <c r="A41" s="13" t="n">
-        <v>46294</v>
-      </c>
-    </row>
-    <row r="42" ht="24" customHeight="1">
-      <c r="A42" s="14" t="inlineStr"/>
-      <c r="K42" s="15" t="inlineStr">
-        <is>
-          <t>현장대리인</t>
-        </is>
-      </c>
-      <c r="Q42" s="16" t="inlineStr">
-        <is>
-          <t>김철수</t>
-        </is>
-      </c>
-      <c r="U42" s="17" t="inlineStr">
-        <is>
-          <t>(서명 또는 인)</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="24" customHeight="1">
-      <c r="A43" s="14" t="inlineStr"/>
-      <c r="K43" s="15" t="inlineStr">
-        <is>
-          <t>안전관리자</t>
-        </is>
-      </c>
-      <c r="Q43" s="16" t="inlineStr">
-        <is>
-          <t>정안전</t>
-        </is>
-      </c>
-      <c r="U43" s="17" t="inlineStr">
-        <is>
-          <t>(서명 또는 인)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="6" customHeight="1"/>
-    <row r="46" ht="19.5" customHeight="1">
-      <c r="A46" s="18" t="inlineStr">
-        <is>
-          <t>이 시트는 작성 예시입니다(가상의 현장 · 이름 · 금액). 실제로는 앞 시트에 적으세요.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="117">
-    <mergeCell ref="I14:L14"/>
-    <mergeCell ref="M18:S18"/>
-    <mergeCell ref="T15:X15"/>
-    <mergeCell ref="E28:J28"/>
-    <mergeCell ref="K34:R34"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="M17:S17"/>
-    <mergeCell ref="A29:D29"/>
-    <mergeCell ref="S28:X28"/>
-    <mergeCell ref="A43:J43"/>
-    <mergeCell ref="E30:J30"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A3:X3"/>
-    <mergeCell ref="M19:S19"/>
-    <mergeCell ref="A31:D31"/>
-    <mergeCell ref="K29:R29"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="K31:R31"/>
-    <mergeCell ref="S29:X29"/>
-    <mergeCell ref="A38:F38"/>
-    <mergeCell ref="E32:J32"/>
-    <mergeCell ref="I16:L16"/>
-    <mergeCell ref="S31:X31"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="T22:X22"/>
-    <mergeCell ref="A27:D27"/>
-    <mergeCell ref="I18:L18"/>
-    <mergeCell ref="A24:X24"/>
-    <mergeCell ref="M13:S13"/>
-    <mergeCell ref="M21:S21"/>
-    <mergeCell ref="A33:D33"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="U42:X42"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="G7:X7"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="G38:X38"/>
-    <mergeCell ref="T20:X20"/>
-    <mergeCell ref="T14:X14"/>
-    <mergeCell ref="K33:R33"/>
-    <mergeCell ref="I20:L20"/>
-    <mergeCell ref="A19:D19"/>
-    <mergeCell ref="E34:J34"/>
-    <mergeCell ref="A28:D28"/>
-    <mergeCell ref="E22:H22"/>
-    <mergeCell ref="I13:L13"/>
-    <mergeCell ref="S34:X34"/>
-    <mergeCell ref="A30:D30"/>
-    <mergeCell ref="E21:H21"/>
-    <mergeCell ref="I15:L15"/>
-    <mergeCell ref="S30:X30"/>
-    <mergeCell ref="E14:H14"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="G9:X9"/>
-    <mergeCell ref="T17:X17"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="T19:X19"/>
-    <mergeCell ref="M15:S15"/>
-    <mergeCell ref="U43:X43"/>
-    <mergeCell ref="A42:J42"/>
-    <mergeCell ref="I17:L17"/>
-    <mergeCell ref="G37:X37"/>
-    <mergeCell ref="E16:H16"/>
-    <mergeCell ref="A41:X41"/>
-    <mergeCell ref="I19:L19"/>
-    <mergeCell ref="K43:P43"/>
-    <mergeCell ref="E18:H18"/>
-    <mergeCell ref="K26:R26"/>
-    <mergeCell ref="A34:D34"/>
-    <mergeCell ref="S33:X33"/>
-    <mergeCell ref="K42:P42"/>
-    <mergeCell ref="E27:J27"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="Q42:T42"/>
-    <mergeCell ref="T21:X21"/>
-    <mergeCell ref="E20:H20"/>
-    <mergeCell ref="K27:R27"/>
-    <mergeCell ref="M20:S20"/>
-    <mergeCell ref="E13:H13"/>
-    <mergeCell ref="T13:X13"/>
-    <mergeCell ref="T16:X16"/>
-    <mergeCell ref="A36:F36"/>
-    <mergeCell ref="I21:L21"/>
-    <mergeCell ref="M22:S22"/>
-    <mergeCell ref="A21:D21"/>
-    <mergeCell ref="G36:X36"/>
-    <mergeCell ref="A11:X11"/>
-    <mergeCell ref="E15:H15"/>
-    <mergeCell ref="K28:R28"/>
-    <mergeCell ref="T18:X18"/>
-    <mergeCell ref="A32:D32"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="E29:J29"/>
-    <mergeCell ref="K30:R30"/>
-    <mergeCell ref="A37:F37"/>
-    <mergeCell ref="E31:J31"/>
-    <mergeCell ref="G6:X6"/>
-    <mergeCell ref="A46:X46"/>
-    <mergeCell ref="M14:S14"/>
-    <mergeCell ref="G5:X5"/>
-    <mergeCell ref="Q43:T43"/>
-    <mergeCell ref="K32:R32"/>
-    <mergeCell ref="E26:J26"/>
-    <mergeCell ref="E17:H17"/>
-    <mergeCell ref="S32:X32"/>
-    <mergeCell ref="S26:X26"/>
-    <mergeCell ref="E19:H19"/>
-    <mergeCell ref="I22:L22"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="E33:J33"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="S27:X27"/>
-    <mergeCell ref="M16:S16"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="M1:X1"/>
-    <mergeCell ref="G8:X8"/>
-  </mergeCells>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/web/public/forms/hyeonjang-jojikdo.xlsx
+++ b/web/public/forms/hyeonjang-jojikdo.xlsx
@@ -576,7 +576,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="M1" s="2" t="inlineStr">
